--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Mission Wrecker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Mission Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D8041BE-1E81-4D1B-AF93-DCA6CAE91814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDBDE68-1BE4-40EC-BCAD-42F0DC4F71EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="23295" windowHeight="13380" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Mission Wrecker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mission Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDBDE68-1BE4-40EC-BCAD-42F0DC4F71EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C766BBE-DDA3-4C92-9CDF-3DB68559193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5600" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5602" uniqueCount="121">
   <si>
     <t>Company Name</t>
   </si>
@@ -32106,7 +32106,7 @@
         <v>46083.754745370374</v>
       </c>
       <c r="J1159">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1159" t="s">
         <v>11</v>
@@ -32135,7 +32135,7 @@
         <v>46083.755439814813</v>
       </c>
       <c r="J1160">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1160" t="s">
         <v>11</v>
@@ -32184,16 +32184,16 @@
         <v>26</v>
       </c>
       <c r="G1162" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1162" s="2">
-        <v>0</v>
+        <v>5.4976851851851853E-3</v>
       </c>
       <c r="I1162" s="1">
         <v>46083.75613425926</v>
       </c>
       <c r="J1162">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1162" t="s">
         <v>11</v>
@@ -32251,7 +32251,7 @@
         <v>46083.756828703707</v>
       </c>
       <c r="J1164">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1164" t="s">
         <v>11</v>
@@ -32280,7 +32280,7 @@
         <v>46083.757523148146</v>
       </c>
       <c r="J1165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1165" t="s">
         <v>11</v>
@@ -32309,7 +32309,7 @@
         <v>46083.758217592593</v>
       </c>
       <c r="J1166">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1166" t="s">
         <v>11</v>
@@ -32396,7 +32396,7 @@
         <v>46083.759606481479</v>
       </c>
       <c r="J1169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1169" t="s">
         <v>11</v>
@@ -32474,16 +32474,16 @@
         <v>26</v>
       </c>
       <c r="G1172" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1172" s="2">
-        <v>0</v>
+        <v>4.6759259259259263E-3</v>
       </c>
       <c r="I1172" s="1">
         <v>46083.760300925926</v>
       </c>
       <c r="J1172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1172" t="s">
         <v>11</v>
@@ -32570,7 +32570,7 @@
         <v>46083.761689814812</v>
       </c>
       <c r="J1175">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1175" t="s">
         <v>11</v>
@@ -32599,7 +32599,7 @@
         <v>46083.762384259258</v>
       </c>
       <c r="J1176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1176" t="s">
         <v>11</v>
@@ -32628,7 +32628,7 @@
         <v>46083.763078703705</v>
       </c>
       <c r="J1177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1177" t="s">
         <v>11</v>
@@ -32686,7 +32686,7 @@
         <v>46083.763773148145</v>
       </c>
       <c r="J1179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1179" t="s">
         <v>11</v>
@@ -32744,7 +32744,7 @@
         <v>46083.765162037038</v>
       </c>
       <c r="J1181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1181" t="s">
         <v>11</v>
@@ -32802,7 +32802,7 @@
         <v>46083.765856481485</v>
       </c>
       <c r="J1183">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1183" t="s">
         <v>11</v>
@@ -32918,7 +32918,7 @@
         <v>46083.767939814818</v>
       </c>
       <c r="J1187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1187" t="s">
         <v>11</v>
@@ -32967,16 +32967,16 @@
         <v>26</v>
       </c>
       <c r="G1189" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1189" s="2">
-        <v>0</v>
+        <v>3.8981481481481478E-2</v>
       </c>
       <c r="I1189" s="1">
         <v>46083.768634259257</v>
       </c>
       <c r="J1189">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1189" t="s">
         <v>11</v>
@@ -33063,7 +33063,7 @@
         <v>46083.77002314815</v>
       </c>
       <c r="J1192">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1192" t="s">
         <v>11</v>
@@ -33083,84 +33083,62 @@
         <v>26</v>
       </c>
       <c r="G1193" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1193" s="2">
-        <v>0</v>
+        <v>1.6666666666666668E-3</v>
       </c>
       <c r="I1193" s="1">
         <v>46083.77002314815</v>
       </c>
       <c r="J1193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1193" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1194" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1194" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1194">
+      <c r="H1194" s="2"/>
+      <c r="I1194" s="1"/>
+      <c r="K1194" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1195" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1195" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1195">
         <v>3759</v>
       </c>
-      <c r="D1194" t="s">
+      <c r="D1195" t="s">
         <v>110</v>
       </c>
-      <c r="F1194" t="s">
+      <c r="F1195" t="s">
         <v>26</v>
       </c>
-      <c r="G1194" t="s">
+      <c r="G1195" t="s">
         <v>14</v>
       </c>
-      <c r="H1194" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1194" s="1">
+      <c r="H1195" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1195" s="1">
         <v>46083.77071759259</v>
       </c>
-      <c r="J1194">
-        <v>0</v>
-      </c>
-      <c r="K1194" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1195" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1195" s="2"/>
-      <c r="I1195" s="1"/>
+      <c r="J1195">
+        <v>0</v>
+      </c>
       <c r="K1195" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1196" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1196" s="2"/>
+      <c r="I1196" s="1"/>
+      <c r="K1196" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="1196" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1196" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1196">
-        <v>901</v>
-      </c>
-      <c r="D1196" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1196" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1196" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1196" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1196" s="1">
-        <v>46083.771412037036</v>
-      </c>
-      <c r="J1196">
-        <v>2</v>
-      </c>
-      <c r="K1196" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1197" spans="2:11" x14ac:dyDescent="0.25">
@@ -33168,25 +33146,25 @@
         <v>35</v>
       </c>
       <c r="C1197">
-        <v>972</v>
+        <v>901</v>
       </c>
       <c r="D1197" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F1197" t="s">
         <v>26</v>
       </c>
       <c r="G1197" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1197" s="2">
-        <v>4.8032407407407407E-3</v>
+        <v>0</v>
       </c>
       <c r="I1197" s="1">
         <v>46083.771412037036</v>
       </c>
       <c r="J1197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1197" t="s">
         <v>11</v>
@@ -33197,22 +33175,22 @@
         <v>35</v>
       </c>
       <c r="C1198">
-        <v>2808</v>
+        <v>972</v>
       </c>
       <c r="D1198" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="F1198" t="s">
         <v>26</v>
       </c>
       <c r="G1198" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1198" s="2">
-        <v>0</v>
+        <v>4.8032407407407407E-3</v>
       </c>
       <c r="I1198" s="1">
-        <v>46083.772106481483</v>
+        <v>46083.771412037036</v>
       </c>
       <c r="J1198">
         <v>2</v>
@@ -33226,10 +33204,10 @@
         <v>35</v>
       </c>
       <c r="C1199">
-        <v>5099</v>
+        <v>2808</v>
       </c>
       <c r="D1199" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="F1199" t="s">
         <v>26</v>
@@ -33244,7 +33222,7 @@
         <v>46083.772106481483</v>
       </c>
       <c r="J1199">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1199" t="s">
         <v>11</v>
@@ -33255,25 +33233,25 @@
         <v>35</v>
       </c>
       <c r="C1200">
-        <v>975</v>
+        <v>5099</v>
       </c>
       <c r="D1200" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="F1200" t="s">
         <v>26</v>
       </c>
       <c r="G1200" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1200" s="2">
-        <v>0</v>
+        <v>4.6759259259259263E-3</v>
       </c>
       <c r="I1200" s="1">
-        <v>46083.772800925923</v>
+        <v>46083.772106481483</v>
       </c>
       <c r="J1200">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1200" t="s">
         <v>11</v>
@@ -33284,10 +33262,10 @@
         <v>35</v>
       </c>
       <c r="C1201">
-        <v>2806</v>
+        <v>975</v>
       </c>
       <c r="D1201" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="F1201" t="s">
         <v>26</v>
@@ -33299,10 +33277,10 @@
         <v>0</v>
       </c>
       <c r="I1201" s="1">
-        <v>46083.773495370369</v>
+        <v>46083.772800925923</v>
       </c>
       <c r="J1201">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1201" t="s">
         <v>11</v>
@@ -33313,25 +33291,25 @@
         <v>35</v>
       </c>
       <c r="C1202">
-        <v>3833</v>
+        <v>2806</v>
       </c>
       <c r="D1202" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F1202" t="s">
         <v>26</v>
       </c>
       <c r="G1202" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1202" s="2">
-        <v>5.6481481481481478E-3</v>
+        <v>0</v>
       </c>
       <c r="I1202" s="1">
         <v>46083.773495370369</v>
       </c>
       <c r="J1202">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1202" t="s">
         <v>11</v>
@@ -33342,37 +33320,65 @@
         <v>35</v>
       </c>
       <c r="C1203">
-        <v>5098</v>
+        <v>3833</v>
       </c>
       <c r="D1203" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F1203" t="s">
         <v>26</v>
       </c>
       <c r="G1203" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1203" s="2">
-        <v>0</v>
+        <v>5.6481481481481478E-3</v>
       </c>
       <c r="I1203" s="1">
+        <v>46083.773495370369</v>
+      </c>
+      <c r="J1203">
+        <v>0</v>
+      </c>
+      <c r="K1203" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1204" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1204" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1204">
+        <v>5098</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1204" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1204" s="2">
+        <v>4.8125000000000001E-2</v>
+      </c>
+      <c r="I1204" s="1">
         <v>46083.774189814816</v>
       </c>
-      <c r="J1203">
-        <v>2</v>
-      </c>
-      <c r="K1203" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1204" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1204" s="2"/>
-      <c r="I1204" s="1"/>
+      <c r="J1204">
+        <v>3</v>
+      </c>
+      <c r="K1204" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1205" s="2"/>
       <c r="I1205" s="1"/>
+      <c r="K1205" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="1206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1206" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mission Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C766BBE-DDA3-4C92-9CDF-3DB68559193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573EF795-AE40-4A49-84E7-D328FAB4EA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -32970,7 +32970,7 @@
         <v>10</v>
       </c>
       <c r="H1189" s="2">
-        <v>3.8981481481481478E-2</v>
+        <v>4.1793981481481481E-2</v>
       </c>
       <c r="I1189" s="1">
         <v>46083.768634259257</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mission Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573EF795-AE40-4A49-84E7-D328FAB4EA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9263AF-F39F-495C-86C3-4D5593D18577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5602" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5824" uniqueCount="122">
   <si>
     <t>Company Name</t>
   </si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>Wyatt Hankinson</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -33381,235 +33384,1342 @@
       </c>
     </row>
     <row r="1206" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1206" s="2"/>
-      <c r="I1206" s="1"/>
+      <c r="B1206" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1206">
+        <v>900</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1206" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1206" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1206" s="1">
+        <v>46118.797337962962</v>
+      </c>
+      <c r="J1206">
+        <v>1</v>
+      </c>
+      <c r="K1206" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1207" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1207" s="2"/>
-      <c r="I1207" s="1"/>
+      <c r="B1207" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1207">
+        <v>908</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1207" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1207" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1207" s="1">
+        <v>46118.797337962962</v>
+      </c>
+      <c r="J1207">
+        <v>1</v>
+      </c>
+      <c r="K1207" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1208" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1208" s="2"/>
-      <c r="I1208" s="1"/>
+      <c r="B1208" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1208">
+        <v>866</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1208" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1208" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1208" s="2">
+        <v>7.743055555555556E-3</v>
+      </c>
+      <c r="I1208" s="1">
+        <v>46118.798032407409</v>
+      </c>
+      <c r="J1208">
+        <v>1</v>
+      </c>
+      <c r="K1208" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1209" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1209" s="2"/>
-      <c r="I1209" s="1"/>
+      <c r="B1209" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1209">
+        <v>3139</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1209" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1209" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1209" s="1">
+        <v>46118.798726851855</v>
+      </c>
+      <c r="J1209">
+        <v>1</v>
+      </c>
+      <c r="K1209" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1210" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1210" s="2"/>
-      <c r="I1210" s="1"/>
+      <c r="B1210" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1210">
+        <v>897</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1210" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1210" s="2">
+        <v>1.2592592592592593E-2</v>
+      </c>
+      <c r="I1210" s="1">
+        <v>46118.798726851855</v>
+      </c>
+      <c r="J1210">
+        <v>1</v>
+      </c>
+      <c r="K1210" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1211" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1211" s="2"/>
-      <c r="I1211" s="1"/>
+      <c r="B1211" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1211">
+        <v>5045</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1211" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1211" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1211" s="1">
+        <v>46118.799421296295</v>
+      </c>
+      <c r="J1211">
+        <v>1</v>
+      </c>
+      <c r="K1211" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1212" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1212" s="2"/>
-      <c r="I1212" s="1"/>
+      <c r="B1212" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1212">
+        <v>2804</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1212" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1212" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1212" s="1">
+        <v>46118.799421296295</v>
+      </c>
+      <c r="J1212">
+        <v>1</v>
+      </c>
+      <c r="K1212" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1213" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1213" s="2"/>
-      <c r="I1213" s="1"/>
+      <c r="B1213" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1213">
+        <v>5100</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1213" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1213" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1213" s="1">
+        <v>46118.800115740742</v>
+      </c>
+      <c r="J1213">
+        <v>1</v>
+      </c>
+      <c r="K1213" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1214" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1214" s="2"/>
-      <c r="I1214" s="1"/>
+      <c r="B1214" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1214">
+        <v>875</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1214" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1214" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1214" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1214" s="1">
+        <v>46118.800810185188</v>
+      </c>
+      <c r="J1214">
+        <v>1</v>
+      </c>
+      <c r="K1214" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1215" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1215" s="2"/>
-      <c r="I1215" s="1"/>
+      <c r="B1215" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1215">
+        <v>4882</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1215" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1215" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1215" s="1">
+        <v>46118.800810185188</v>
+      </c>
+      <c r="J1215">
+        <v>1</v>
+      </c>
+      <c r="K1215" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1216" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1216" s="2"/>
-      <c r="I1216" s="1"/>
-    </row>
-    <row r="1217" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1217" s="2"/>
-      <c r="I1217" s="1"/>
-    </row>
-    <row r="1218" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1218" s="2"/>
-      <c r="I1218" s="1"/>
-    </row>
-    <row r="1219" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1219" s="2"/>
-      <c r="I1219" s="1"/>
-    </row>
-    <row r="1220" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1220" s="2"/>
-      <c r="I1220" s="1"/>
-    </row>
-    <row r="1221" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1221" s="2"/>
-      <c r="I1221" s="1"/>
-    </row>
-    <row r="1222" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1222" s="2"/>
-      <c r="I1222" s="1"/>
-    </row>
-    <row r="1223" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1223" s="2"/>
-      <c r="I1223" s="1"/>
-    </row>
-    <row r="1224" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1224" s="2"/>
-      <c r="I1224" s="1"/>
-    </row>
-    <row r="1225" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1225" s="2"/>
-      <c r="I1225" s="1"/>
-    </row>
-    <row r="1226" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1226" s="2"/>
-      <c r="I1226" s="1"/>
-    </row>
-    <row r="1227" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1227" s="2"/>
-      <c r="I1227" s="1"/>
-    </row>
-    <row r="1228" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1228" s="2"/>
-      <c r="I1228" s="1"/>
-    </row>
-    <row r="1229" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1229" s="2"/>
-      <c r="I1229" s="1"/>
-    </row>
-    <row r="1230" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1230" s="2"/>
-      <c r="I1230" s="1"/>
-    </row>
-    <row r="1231" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1231" s="2"/>
-      <c r="I1231" s="1"/>
-    </row>
-    <row r="1232" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1232" s="2"/>
-      <c r="I1232" s="1"/>
-    </row>
-    <row r="1233" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B1216" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1216">
+        <v>979</v>
+      </c>
+      <c r="D1216" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1216" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1216" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1216" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1216" s="1">
+        <v>46118.801504629628</v>
+      </c>
+      <c r="J1216">
+        <v>1</v>
+      </c>
+      <c r="K1216" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1217" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1217" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1217">
+        <v>971</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1217" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1217" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1217" s="2">
+        <v>6.8402777777777776E-3</v>
+      </c>
+      <c r="I1217" s="1">
+        <v>46118.802199074074</v>
+      </c>
+      <c r="J1217">
+        <v>1</v>
+      </c>
+      <c r="K1217" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1218" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1218" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1218">
+        <v>903</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1218" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1218" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1218" s="2">
+        <v>8.0902777777777778E-3</v>
+      </c>
+      <c r="I1218" s="1">
+        <v>46118.802199074074</v>
+      </c>
+      <c r="J1218">
+        <v>1</v>
+      </c>
+      <c r="K1218" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1219" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1219" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1219">
+        <v>910</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1219" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1219" s="2">
+        <v>7.083333333333333E-3</v>
+      </c>
+      <c r="I1219" s="1">
+        <v>46118.802893518521</v>
+      </c>
+      <c r="J1219">
+        <v>1</v>
+      </c>
+      <c r="K1219" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1220" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1220" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1220">
+        <v>909</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1220" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1220" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1220" s="1">
+        <v>46118.803587962961</v>
+      </c>
+      <c r="J1220">
+        <v>1</v>
+      </c>
+      <c r="K1220" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1221" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1221" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1221">
+        <v>865</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1221" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1221" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1221" s="1">
+        <v>46118.803587962961</v>
+      </c>
+      <c r="J1221">
+        <v>1</v>
+      </c>
+      <c r="K1221" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1222" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1222" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1222">
+        <v>880</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1222" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1222" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1222" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1222" s="1">
+        <v>46118.804282407407</v>
+      </c>
+      <c r="J1222">
+        <v>1</v>
+      </c>
+      <c r="K1222" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1223" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1223" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1223">
+        <v>860</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1223" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1223" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1223" s="2">
+        <v>1.4398148148148148E-2</v>
+      </c>
+      <c r="I1223" s="1">
+        <v>46118.804976851854</v>
+      </c>
+      <c r="J1223">
+        <v>1</v>
+      </c>
+      <c r="K1223" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1224" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1224" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1224">
+        <v>864</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1224" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1224" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1224" s="1">
+        <v>46118.804976851854</v>
+      </c>
+      <c r="J1224">
+        <v>1</v>
+      </c>
+      <c r="K1224" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1225" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1225" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1225">
+        <v>886</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1225" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1225" s="2">
+        <v>7.3032407407407404E-3</v>
+      </c>
+      <c r="I1225" s="1">
+        <v>46118.805671296293</v>
+      </c>
+      <c r="J1225">
+        <v>0</v>
+      </c>
+      <c r="K1225" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1226" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1226" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1226">
+        <v>4959</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1226" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1226" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1226" s="1">
+        <v>46118.805671296293</v>
+      </c>
+      <c r="J1226">
+        <v>1</v>
+      </c>
+      <c r="K1226" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1227" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1227" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1227">
+        <v>876</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1227" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1227" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1227" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1227" s="1">
+        <v>46118.80636574074</v>
+      </c>
+      <c r="J1227">
+        <v>1</v>
+      </c>
+      <c r="K1227" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1228" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1228" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1228">
+        <v>3261</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1228" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1228" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1228" s="1">
+        <v>46118.807060185187</v>
+      </c>
+      <c r="J1228">
+        <v>1</v>
+      </c>
+      <c r="K1228" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1229" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1229" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1229">
+        <v>977</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1229" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1229" s="2">
+        <v>8.1712962962962963E-3</v>
+      </c>
+      <c r="I1229" s="1">
+        <v>46118.807060185187</v>
+      </c>
+      <c r="J1229">
+        <v>1</v>
+      </c>
+      <c r="K1229" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1230" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1230" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1230">
+        <v>4888</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1230" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1230" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1230" s="1">
+        <v>46118.807754629626</v>
+      </c>
+      <c r="J1230">
+        <v>1</v>
+      </c>
+      <c r="K1230" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1231" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1231" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1231">
+        <v>888</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1231" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1231" s="2">
+        <v>7.5462962962962966E-3</v>
+      </c>
+      <c r="I1231" s="1">
+        <v>46118.807754629626</v>
+      </c>
+      <c r="J1231">
+        <v>1</v>
+      </c>
+      <c r="K1231" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1232" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1232" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1232">
+        <v>871</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1232" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1232" s="2">
+        <v>2.8472222222222223E-3</v>
+      </c>
+      <c r="I1232" s="1">
+        <v>46118.808449074073</v>
+      </c>
+      <c r="J1232">
+        <v>0</v>
+      </c>
+      <c r="K1232" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
-    </row>
-    <row r="1234" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1234" s="2"/>
-      <c r="I1234" s="1"/>
-    </row>
-    <row r="1235" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1235" s="2"/>
-      <c r="I1235" s="1"/>
-    </row>
-    <row r="1236" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1236" s="2"/>
-      <c r="I1236" s="1"/>
-    </row>
-    <row r="1237" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1237" s="2"/>
-      <c r="I1237" s="1"/>
-    </row>
-    <row r="1238" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1238" s="2"/>
-      <c r="I1238" s="1"/>
-    </row>
-    <row r="1239" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1239" s="2"/>
-      <c r="I1239" s="1"/>
-    </row>
-    <row r="1240" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1240" s="2"/>
-      <c r="I1240" s="1"/>
-    </row>
-    <row r="1241" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1241" s="2"/>
-      <c r="I1241" s="1"/>
-    </row>
-    <row r="1242" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1242" s="2"/>
-      <c r="I1242" s="1"/>
-    </row>
-    <row r="1243" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1243" s="2"/>
-      <c r="I1243" s="1"/>
-    </row>
-    <row r="1244" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1244" s="2"/>
-      <c r="I1244" s="1"/>
-    </row>
-    <row r="1245" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1245" s="2"/>
-      <c r="I1245" s="1"/>
-    </row>
-    <row r="1246" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1246" s="2"/>
-      <c r="I1246" s="1"/>
-    </row>
-    <row r="1247" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1247" s="2"/>
-      <c r="I1247" s="1"/>
-    </row>
-    <row r="1248" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1248" s="1"/>
-    </row>
-    <row r="1249" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1249" s="2"/>
-      <c r="I1249" s="1"/>
-    </row>
-    <row r="1250" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1250" s="2"/>
-      <c r="I1250" s="1"/>
-    </row>
-    <row r="1251" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1233" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1234" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1234" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1234">
+        <v>873</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1234" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1234" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1234" s="2">
+        <v>8.8078703703703704E-3</v>
+      </c>
+      <c r="I1234" s="1">
+        <v>46118.80914351852</v>
+      </c>
+      <c r="J1234">
+        <v>0</v>
+      </c>
+      <c r="K1234" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1235" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1235" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1235">
+        <v>5097</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1235" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1235" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1235" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1235" s="1">
+        <v>46118.80914351852</v>
+      </c>
+      <c r="J1235">
+        <v>1</v>
+      </c>
+      <c r="K1235" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1236" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1236" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1236">
+        <v>2800</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1236" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1236" s="2">
+        <v>7.4421296296296293E-3</v>
+      </c>
+      <c r="I1236" s="1">
+        <v>46118.809837962966</v>
+      </c>
+      <c r="J1236">
+        <v>1</v>
+      </c>
+      <c r="K1236" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1237" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1237" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1237">
+        <v>891</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1237" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1237" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1237" s="1">
+        <v>46118.810532407406</v>
+      </c>
+      <c r="J1237">
+        <v>1</v>
+      </c>
+      <c r="K1237" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1238" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1238" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1238">
+        <v>898</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1238" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1238" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1238" s="1">
+        <v>46118.810532407406</v>
+      </c>
+      <c r="J1238">
+        <v>1</v>
+      </c>
+      <c r="K1238" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1239" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1239" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1239">
+        <v>905</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1239" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1239" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1239" s="1">
+        <v>46118.811226851853</v>
+      </c>
+      <c r="J1239">
+        <v>1</v>
+      </c>
+      <c r="K1239" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1240" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1240" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1240">
+        <v>894</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1240" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1240" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1240" s="1">
+        <v>46118.811226851853</v>
+      </c>
+      <c r="J1240">
+        <v>1</v>
+      </c>
+      <c r="K1240" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1241" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1241" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1241">
+        <v>896</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1241" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1241" s="2">
+        <v>6.6203703703703702E-3</v>
+      </c>
+      <c r="I1241" s="1">
+        <v>46118.811921296299</v>
+      </c>
+      <c r="J1241">
+        <v>1</v>
+      </c>
+      <c r="K1241" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1242" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1242" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1242">
+        <v>3759</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1242" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1242" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1242" s="1">
+        <v>46118.812615740739</v>
+      </c>
+      <c r="J1242">
+        <v>1</v>
+      </c>
+      <c r="K1242" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1243" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1243" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1243">
+        <v>901</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1243" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1243" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1243" s="1">
+        <v>46118.812615740739</v>
+      </c>
+      <c r="J1243">
+        <v>1</v>
+      </c>
+      <c r="K1243" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1244" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1244" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1244">
+        <v>972</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1244" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1244" s="2">
+        <v>7.6736111111111111E-3</v>
+      </c>
+      <c r="I1244" s="1">
+        <v>46118.813310185185</v>
+      </c>
+      <c r="J1244">
+        <v>1</v>
+      </c>
+      <c r="K1244" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1245" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1245" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1245">
+        <v>2808</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1245" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1245" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1245" s="1">
+        <v>46118.813310185185</v>
+      </c>
+      <c r="J1245">
+        <v>1</v>
+      </c>
+      <c r="K1245" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1246" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1246" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1246">
+        <v>5099</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1246" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1246" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1246" s="1">
+        <v>46118.814004629632</v>
+      </c>
+      <c r="J1246">
+        <v>1</v>
+      </c>
+      <c r="K1246" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1247" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1247" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1247">
+        <v>975</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1247" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1247" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1247" s="1">
+        <v>46118.814004629632</v>
+      </c>
+      <c r="J1247">
+        <v>1</v>
+      </c>
+      <c r="K1247" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1248" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1248" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1248">
+        <v>2806</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1248" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1248">
+        <v>0</v>
+      </c>
+      <c r="I1248" s="1">
+        <v>46118.793981481482</v>
+      </c>
+      <c r="J1248">
+        <v>1</v>
+      </c>
+      <c r="K1248" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1249" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1249" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1249">
+        <v>3833</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1249" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1249" s="2">
+        <v>8.3449074074074068E-3</v>
+      </c>
+      <c r="I1249" s="1">
+        <v>46118.793981481482</v>
+      </c>
+      <c r="J1249">
+        <v>1</v>
+      </c>
+      <c r="K1249" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1250" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1250" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1250">
+        <v>5098</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1250" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1250" s="2">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="I1250" s="1">
+        <v>46118.794675925928</v>
+      </c>
+      <c r="J1250">
+        <v>1</v>
+      </c>
+      <c r="K1250" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1251" s="2"/>
       <c r="I1251" s="1"/>
-    </row>
-    <row r="1252" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1251" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1252" s="2"/>
       <c r="I1252" s="1"/>
     </row>
-    <row r="1253" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1253" s="2"/>
       <c r="I1253" s="1"/>
     </row>
-    <row r="1254" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1254" s="2"/>
       <c r="I1254" s="1"/>
     </row>
-    <row r="1255" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1255" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1255" s="2"/>
       <c r="I1255" s="1"/>
     </row>
-    <row r="1256" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1256" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
     </row>
-    <row r="1257" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1257" s="2"/>
       <c r="I1257" s="1"/>
     </row>
-    <row r="1258" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1258" s="1"/>
     </row>
-    <row r="1259" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1259" s="2"/>
       <c r="I1259" s="1"/>
     </row>
-    <row r="1260" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1260" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1260" s="2"/>
       <c r="I1260" s="1"/>
     </row>
-    <row r="1261" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1261" s="1"/>
     </row>
-    <row r="1262" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1262" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1262" s="2"/>
       <c r="I1262" s="1"/>
     </row>
-    <row r="1263" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1263" s="2"/>
       <c r="I1263" s="1"/>
     </row>
-    <row r="1264" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1264" s="2"/>
       <c r="I1264" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mission Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9263AF-F39F-495C-86C3-4D5593D18577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBAAFD2-DFF7-4A81-9791-B078EF5198BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -33406,7 +33406,7 @@
         <v>46118.797337962962</v>
       </c>
       <c r="J1206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1206" t="s">
         <v>11</v>
@@ -33435,7 +33435,7 @@
         <v>46118.797337962962</v>
       </c>
       <c r="J1207">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1207" t="s">
         <v>11</v>
@@ -33493,7 +33493,7 @@
         <v>46118.798726851855</v>
       </c>
       <c r="J1209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1209" t="s">
         <v>11</v>
@@ -33551,7 +33551,7 @@
         <v>46118.799421296295</v>
       </c>
       <c r="J1211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1211" t="s">
         <v>11</v>
@@ -33580,7 +33580,7 @@
         <v>46118.799421296295</v>
       </c>
       <c r="J1212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1212" t="s">
         <v>11</v>
@@ -33609,7 +33609,7 @@
         <v>46118.800115740742</v>
       </c>
       <c r="J1213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1213" t="s">
         <v>11</v>
@@ -33629,16 +33629,16 @@
         <v>121</v>
       </c>
       <c r="G1214" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1214" s="2">
-        <v>0</v>
+        <v>9.5949074074074079E-3</v>
       </c>
       <c r="I1214" s="1">
         <v>46118.800810185188</v>
       </c>
       <c r="J1214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1214" t="s">
         <v>11</v>
@@ -33658,16 +33658,16 @@
         <v>121</v>
       </c>
       <c r="G1215" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1215" s="2">
-        <v>0</v>
+        <v>7.6504629629629631E-3</v>
       </c>
       <c r="I1215" s="1">
         <v>46118.800810185188</v>
       </c>
       <c r="J1215">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1215" t="s">
         <v>11</v>
@@ -33696,7 +33696,7 @@
         <v>46118.801504629628</v>
       </c>
       <c r="J1216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1216" t="s">
         <v>11</v>
@@ -33803,16 +33803,16 @@
         <v>121</v>
       </c>
       <c r="G1220" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1220" s="2">
-        <v>0</v>
+        <v>7.013888888888889E-3</v>
       </c>
       <c r="I1220" s="1">
         <v>46118.803587962961</v>
       </c>
       <c r="J1220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1220" t="s">
         <v>11</v>
@@ -33832,16 +33832,16 @@
         <v>121</v>
       </c>
       <c r="G1221" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1221" s="2">
-        <v>0</v>
+        <v>1.0324074074074074E-2</v>
       </c>
       <c r="I1221" s="1">
         <v>46118.803587962961</v>
       </c>
       <c r="J1221">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1221" t="s">
         <v>11</v>
@@ -33870,7 +33870,7 @@
         <v>46118.804282407407</v>
       </c>
       <c r="J1222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1222" t="s">
         <v>11</v>
@@ -33928,7 +33928,7 @@
         <v>46118.804976851854</v>
       </c>
       <c r="J1224">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1224" t="s">
         <v>11</v>
@@ -33986,7 +33986,7 @@
         <v>46118.805671296293</v>
       </c>
       <c r="J1226">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1226" t="s">
         <v>11</v>
@@ -34015,7 +34015,7 @@
         <v>46118.80636574074</v>
       </c>
       <c r="J1227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1227" t="s">
         <v>11</v>
@@ -34035,16 +34035,16 @@
         <v>121</v>
       </c>
       <c r="G1228" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1228" s="2">
-        <v>0</v>
+        <v>3.3101851851851851E-3</v>
       </c>
       <c r="I1228" s="1">
         <v>46118.807060185187</v>
       </c>
       <c r="J1228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1228" t="s">
         <v>11</v>
@@ -34102,7 +34102,7 @@
         <v>46118.807754629626</v>
       </c>
       <c r="J1230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1230" t="s">
         <v>11</v>
@@ -34225,7 +34225,7 @@
         <v>46118.80914351852</v>
       </c>
       <c r="J1235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1235" t="s">
         <v>11</v>
@@ -34283,7 +34283,7 @@
         <v>46118.810532407406</v>
       </c>
       <c r="J1237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1237" t="s">
         <v>11</v>
@@ -34303,16 +34303,16 @@
         <v>121</v>
       </c>
       <c r="G1238" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1238" s="2">
-        <v>0</v>
+        <v>7.6620370370370366E-3</v>
       </c>
       <c r="I1238" s="1">
         <v>46118.810532407406</v>
       </c>
       <c r="J1238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1238" t="s">
         <v>11</v>
@@ -34332,16 +34332,16 @@
         <v>121</v>
       </c>
       <c r="G1239" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1239" s="2">
-        <v>0</v>
+        <v>8.7962962962962968E-3</v>
       </c>
       <c r="I1239" s="1">
         <v>46118.811226851853</v>
       </c>
       <c r="J1239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1239" t="s">
         <v>11</v>
@@ -34361,16 +34361,16 @@
         <v>121</v>
       </c>
       <c r="G1240" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1240" s="2">
-        <v>0</v>
+        <v>6.9560185185185185E-3</v>
       </c>
       <c r="I1240" s="1">
         <v>46118.811226851853</v>
       </c>
       <c r="J1240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1240" t="s">
         <v>11</v>
@@ -34419,16 +34419,16 @@
         <v>121</v>
       </c>
       <c r="G1242" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1242" s="2">
-        <v>0</v>
+        <v>8.6226851851851846E-3</v>
       </c>
       <c r="I1242" s="1">
         <v>46118.812615740739</v>
       </c>
       <c r="J1242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1242" t="s">
         <v>11</v>
@@ -34457,7 +34457,7 @@
         <v>46118.812615740739</v>
       </c>
       <c r="J1243">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1243" t="s">
         <v>11</v>
@@ -34515,7 +34515,7 @@
         <v>46118.813310185185</v>
       </c>
       <c r="J1245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1245" t="s">
         <v>11</v>
@@ -34544,7 +34544,7 @@
         <v>46118.814004629632</v>
       </c>
       <c r="J1246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1246" t="s">
         <v>11</v>
@@ -34573,7 +34573,7 @@
         <v>46118.814004629632</v>
       </c>
       <c r="J1247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1247" t="s">
         <v>11</v>
@@ -34593,16 +34593,16 @@
         <v>121</v>
       </c>
       <c r="G1248" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1248">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1248" s="2">
+        <v>1.5833333333333335E-2</v>
       </c>
       <c r="I1248" s="1">
         <v>46118.793981481482</v>
       </c>
       <c r="J1248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1248" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mission Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBAAFD2-DFF7-4A81-9791-B078EF5198BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119EF438-EBAE-4F60-8377-F4A599638821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33406,7 +33406,7 @@
         <v>46118.797337962962</v>
       </c>
       <c r="J1206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1206" t="s">
         <v>11</v>
@@ -33435,7 +33435,7 @@
         <v>46118.797337962962</v>
       </c>
       <c r="J1207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1207" t="s">
         <v>11</v>
@@ -33493,7 +33493,7 @@
         <v>46118.798726851855</v>
       </c>
       <c r="J1209">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1209" t="s">
         <v>11</v>
@@ -33551,7 +33551,7 @@
         <v>46118.799421296295</v>
       </c>
       <c r="J1211">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1211" t="s">
         <v>11</v>
@@ -33580,7 +33580,7 @@
         <v>46118.799421296295</v>
       </c>
       <c r="J1212">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1212" t="s">
         <v>11</v>
@@ -33609,7 +33609,7 @@
         <v>46118.800115740742</v>
       </c>
       <c r="J1213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1213" t="s">
         <v>11</v>
@@ -33696,7 +33696,7 @@
         <v>46118.801504629628</v>
       </c>
       <c r="J1216">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1216" t="s">
         <v>11</v>
@@ -33870,7 +33870,7 @@
         <v>46118.804282407407</v>
       </c>
       <c r="J1222">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1222" t="s">
         <v>11</v>
@@ -33928,7 +33928,7 @@
         <v>46118.804976851854</v>
       </c>
       <c r="J1224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1224" t="s">
         <v>11</v>
@@ -33986,7 +33986,7 @@
         <v>46118.805671296293</v>
       </c>
       <c r="J1226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1226" t="s">
         <v>11</v>
@@ -34015,7 +34015,7 @@
         <v>46118.80636574074</v>
       </c>
       <c r="J1227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1227" t="s">
         <v>11</v>
@@ -34102,7 +34102,7 @@
         <v>46118.807754629626</v>
       </c>
       <c r="J1230">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1230" t="s">
         <v>11</v>
@@ -34225,7 +34225,7 @@
         <v>46118.80914351852</v>
       </c>
       <c r="J1235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1235" t="s">
         <v>11</v>
@@ -34283,7 +34283,7 @@
         <v>46118.810532407406</v>
       </c>
       <c r="J1237">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1237" t="s">
         <v>11</v>
@@ -34457,7 +34457,7 @@
         <v>46118.812615740739</v>
       </c>
       <c r="J1243">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1243" t="s">
         <v>11</v>
@@ -34515,7 +34515,7 @@
         <v>46118.813310185185</v>
       </c>
       <c r="J1245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1245" t="s">
         <v>11</v>
@@ -34544,7 +34544,7 @@
         <v>46118.814004629632</v>
       </c>
       <c r="J1246">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1246" t="s">
         <v>11</v>
@@ -34573,7 +34573,7 @@
         <v>46118.814004629632</v>
       </c>
       <c r="J1247">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1247" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mission Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119EF438-EBAE-4F60-8377-F4A599638821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC12B27E-DAA0-4D42-BAD8-F6E0F669D628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5824" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6045" uniqueCount="122">
   <si>
     <t>Company Name</t>
   </si>
@@ -33406,7 +33406,7 @@
         <v>46118.797337962962</v>
       </c>
       <c r="J1206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1206" t="s">
         <v>11</v>
@@ -33435,7 +33435,7 @@
         <v>46118.797337962962</v>
       </c>
       <c r="J1207">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1207" t="s">
         <v>11</v>
@@ -33493,7 +33493,7 @@
         <v>46118.798726851855</v>
       </c>
       <c r="J1209">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1209" t="s">
         <v>11</v>
@@ -33551,7 +33551,7 @@
         <v>46118.799421296295</v>
       </c>
       <c r="J1211">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1211" t="s">
         <v>11</v>
@@ -33580,7 +33580,7 @@
         <v>46118.799421296295</v>
       </c>
       <c r="J1212">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1212" t="s">
         <v>11</v>
@@ -33609,7 +33609,7 @@
         <v>46118.800115740742</v>
       </c>
       <c r="J1213">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1213" t="s">
         <v>11</v>
@@ -33687,16 +33687,16 @@
         <v>121</v>
       </c>
       <c r="G1216" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1216" s="2">
-        <v>0</v>
+        <v>3.1597222222222222E-3</v>
       </c>
       <c r="I1216" s="1">
         <v>46118.801504629628</v>
       </c>
       <c r="J1216">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1216" t="s">
         <v>11</v>
@@ -33870,7 +33870,7 @@
         <v>46118.804282407407</v>
       </c>
       <c r="J1222">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1222" t="s">
         <v>11</v>
@@ -33928,7 +33928,7 @@
         <v>46118.804976851854</v>
       </c>
       <c r="J1224">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1224" t="s">
         <v>11</v>
@@ -33986,7 +33986,7 @@
         <v>46118.805671296293</v>
       </c>
       <c r="J1226">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1226" t="s">
         <v>11</v>
@@ -34015,7 +34015,7 @@
         <v>46118.80636574074</v>
       </c>
       <c r="J1227">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1227" t="s">
         <v>11</v>
@@ -34102,7 +34102,7 @@
         <v>46118.807754629626</v>
       </c>
       <c r="J1230">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1230" t="s">
         <v>11</v>
@@ -34225,7 +34225,7 @@
         <v>46118.80914351852</v>
       </c>
       <c r="J1235">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1235" t="s">
         <v>11</v>
@@ -34274,10 +34274,10 @@
         <v>121</v>
       </c>
       <c r="G1237" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1237" s="2">
-        <v>0</v>
+        <v>9.7453703703703695E-3</v>
       </c>
       <c r="I1237" s="1">
         <v>46118.810532407406</v>
@@ -34457,7 +34457,7 @@
         <v>46118.812615740739</v>
       </c>
       <c r="J1243">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1243" t="s">
         <v>11</v>
@@ -34515,7 +34515,7 @@
         <v>46118.813310185185</v>
       </c>
       <c r="J1245">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1245" t="s">
         <v>11</v>
@@ -34544,7 +34544,7 @@
         <v>46118.814004629632</v>
       </c>
       <c r="J1246">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1246" t="s">
         <v>11</v>
@@ -34573,7 +34573,7 @@
         <v>46118.814004629632</v>
       </c>
       <c r="J1247">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1247" t="s">
         <v>11</v>
@@ -34674,181 +34674,1287 @@
       </c>
     </row>
     <row r="1252" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1252" s="2"/>
-      <c r="I1252" s="1"/>
+      <c r="B1252" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1252">
+        <v>900</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1252" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1252" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1252" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1252" s="1">
+        <v>46146.687152777777</v>
+      </c>
+      <c r="J1252">
+        <v>0</v>
+      </c>
+      <c r="K1252" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1253" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1253" s="2"/>
-      <c r="I1253" s="1"/>
+      <c r="B1253" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1253">
+        <v>908</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1253" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1253" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1253" s="1">
+        <v>46146.687847222223</v>
+      </c>
+      <c r="J1253">
+        <v>0</v>
+      </c>
+      <c r="K1253" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1254" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1254" s="2"/>
-      <c r="I1254" s="1"/>
+      <c r="B1254" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1254">
+        <v>866</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1254" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1254" s="2">
+        <v>5.6712962962962967E-3</v>
+      </c>
+      <c r="I1254" s="1">
+        <v>46146.68854166667</v>
+      </c>
+      <c r="J1254">
+        <v>0</v>
+      </c>
+      <c r="K1254" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1255" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1255" s="2"/>
-      <c r="I1255" s="1"/>
+      <c r="B1255" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1255">
+        <v>3139</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1255" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1255" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1255" s="1">
+        <v>46146.68854166667</v>
+      </c>
+      <c r="J1255">
+        <v>0</v>
+      </c>
+      <c r="K1255" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1256" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1256" s="2"/>
-      <c r="I1256" s="1"/>
+      <c r="B1256" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1256">
+        <v>897</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1256" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1256" s="2">
+        <v>5.9722222222222225E-3</v>
+      </c>
+      <c r="I1256" s="1">
+        <v>46146.689236111109</v>
+      </c>
+      <c r="J1256">
+        <v>0</v>
+      </c>
+      <c r="K1256" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1257" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1257" s="2"/>
-      <c r="I1257" s="1"/>
+      <c r="B1257" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1257">
+        <v>5045</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1257" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1257" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1257" s="1">
+        <v>46146.689930555556</v>
+      </c>
+      <c r="J1257">
+        <v>0</v>
+      </c>
+      <c r="K1257" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1258" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I1258" s="1"/>
+      <c r="B1258" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1258">
+        <v>2804</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1258" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1258">
+        <v>0</v>
+      </c>
+      <c r="I1258" s="1">
+        <v>46146.689930555556</v>
+      </c>
+      <c r="J1258">
+        <v>0</v>
+      </c>
+      <c r="K1258" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1259" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1259" s="2"/>
-      <c r="I1259" s="1"/>
+      <c r="B1259" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1259">
+        <v>5100</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1259" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1259" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1259" s="1">
+        <v>46146.690625000003</v>
+      </c>
+      <c r="J1259">
+        <v>0</v>
+      </c>
+      <c r="K1259" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1260" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1260" s="2"/>
-      <c r="I1260" s="1"/>
+      <c r="B1260" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1260">
+        <v>875</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1260" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1260" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1260" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1260" s="1">
+        <v>46146.690625000003</v>
+      </c>
+      <c r="J1260">
+        <v>0</v>
+      </c>
+      <c r="K1260" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1261" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I1261" s="1"/>
+      <c r="B1261" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1261">
+        <v>4882</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1261" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1261" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1261">
+        <v>0</v>
+      </c>
+      <c r="I1261" s="1">
+        <v>46146.66851851852</v>
+      </c>
+      <c r="J1261">
+        <v>0</v>
+      </c>
+      <c r="K1261" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1262" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1262" s="2"/>
-      <c r="I1262" s="1"/>
+      <c r="B1262" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1262">
+        <v>979</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1262" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1262" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1262" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1262" s="1">
+        <v>46146.669212962966</v>
+      </c>
+      <c r="J1262">
+        <v>0</v>
+      </c>
+      <c r="K1262" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1263" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1263" s="2"/>
-      <c r="I1263" s="1"/>
+      <c r="B1263" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1263">
+        <v>971</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1263" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1263" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1263" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1263" s="1">
+        <v>46146.669907407406</v>
+      </c>
+      <c r="J1263">
+        <v>0</v>
+      </c>
+      <c r="K1263" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1264" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1264" s="2"/>
-      <c r="I1264" s="1"/>
-    </row>
-    <row r="1265" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1265" s="2"/>
-      <c r="I1265" s="1"/>
-    </row>
-    <row r="1266" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1266" s="2"/>
-      <c r="I1266" s="1"/>
-    </row>
-    <row r="1267" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1267" s="2"/>
-      <c r="I1267" s="1"/>
-    </row>
-    <row r="1268" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B1264" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1264">
+        <v>903</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1264" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1264" s="2">
+        <v>5.1041666666666666E-3</v>
+      </c>
+      <c r="I1264" s="1">
+        <v>46146.670601851853</v>
+      </c>
+      <c r="J1264">
+        <v>0</v>
+      </c>
+      <c r="K1264" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1265" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1265" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1265">
+        <v>910</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1265" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1265" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1265" s="1">
+        <v>46146.670601851853</v>
+      </c>
+      <c r="J1265">
+        <v>0</v>
+      </c>
+      <c r="K1265" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1266" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1266" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1266">
+        <v>909</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1266" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1266" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1266" s="1">
+        <v>46146.671296296299</v>
+      </c>
+      <c r="J1266">
+        <v>0</v>
+      </c>
+      <c r="K1266" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1267" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1267" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1267">
+        <v>865</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1267" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1267" s="2">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="I1267" s="1">
+        <v>46146.671296296299</v>
+      </c>
+      <c r="J1267">
+        <v>0</v>
+      </c>
+      <c r="K1267" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1268" s="2"/>
       <c r="I1268" s="1"/>
-    </row>
-    <row r="1269" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1269" s="2"/>
-      <c r="I1269" s="1"/>
-    </row>
-    <row r="1270" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1270" s="2"/>
-      <c r="I1270" s="1"/>
-    </row>
-    <row r="1271" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1271" s="2"/>
-      <c r="I1271" s="1"/>
-    </row>
-    <row r="1272" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1272" s="2"/>
-      <c r="I1272" s="1"/>
-    </row>
-    <row r="1273" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1273" s="2"/>
-      <c r="I1273" s="1"/>
-    </row>
-    <row r="1274" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1274" s="1"/>
-    </row>
-    <row r="1275" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1275" s="2"/>
-      <c r="I1275" s="1"/>
-    </row>
-    <row r="1276" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1276" s="2"/>
-      <c r="I1276" s="1"/>
-    </row>
-    <row r="1277" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1277" s="2"/>
-      <c r="I1277" s="1"/>
-    </row>
-    <row r="1278" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1278" s="2"/>
-      <c r="I1278" s="1"/>
-    </row>
-    <row r="1279" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1279" s="2"/>
-      <c r="I1279" s="1"/>
-    </row>
-    <row r="1280" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1280" s="2"/>
-      <c r="I1280" s="1"/>
-    </row>
-    <row r="1281" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1281" s="2"/>
-      <c r="I1281" s="1"/>
-    </row>
-    <row r="1282" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1282" s="2"/>
-      <c r="I1282" s="1"/>
-    </row>
-    <row r="1283" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1283" s="2"/>
-      <c r="I1283" s="1"/>
-    </row>
-    <row r="1284" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1284" s="2"/>
-      <c r="I1284" s="1"/>
-    </row>
-    <row r="1285" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1285" s="2"/>
-      <c r="I1285" s="1"/>
-    </row>
-    <row r="1286" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1286" s="2"/>
-      <c r="I1286" s="1"/>
-    </row>
-    <row r="1287" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1287" s="2"/>
-      <c r="I1287" s="1"/>
-    </row>
-    <row r="1288" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1288" s="2"/>
-      <c r="I1288" s="1"/>
-    </row>
-    <row r="1289" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1289" s="2"/>
-      <c r="I1289" s="1"/>
-    </row>
-    <row r="1290" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1290" s="2"/>
-      <c r="I1290" s="1"/>
-    </row>
-    <row r="1291" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1291" s="2"/>
-      <c r="I1291" s="1"/>
-    </row>
-    <row r="1292" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1292" s="2"/>
-      <c r="I1292" s="1"/>
-    </row>
-    <row r="1293" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1293" s="2"/>
-      <c r="I1293" s="1"/>
-    </row>
-    <row r="1294" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1294" s="2"/>
-      <c r="I1294" s="1"/>
-    </row>
-    <row r="1295" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1295" s="2"/>
-      <c r="I1295" s="1"/>
-    </row>
-    <row r="1296" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1296" s="2"/>
-      <c r="I1296" s="1"/>
+      <c r="K1268" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1269" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1269" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1269">
+        <v>880</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1269" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1269" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1269" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1269" s="1">
+        <v>46146.671990740739</v>
+      </c>
+      <c r="J1269">
+        <v>0</v>
+      </c>
+      <c r="K1269" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1270" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1270" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1270">
+        <v>860</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1270" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1270" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1270" s="2">
+        <v>1.1574074074074073E-2</v>
+      </c>
+      <c r="I1270" s="1">
+        <v>46146.672685185185</v>
+      </c>
+      <c r="J1270">
+        <v>0</v>
+      </c>
+      <c r="K1270" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1271" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1271" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1271">
+        <v>864</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1271" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1271" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1271" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1271" s="1">
+        <v>46146.673379629632</v>
+      </c>
+      <c r="J1271">
+        <v>0</v>
+      </c>
+      <c r="K1271" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1272" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1272" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1272">
+        <v>886</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1272" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1272" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1272" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1272" s="1">
+        <v>46146.674074074072</v>
+      </c>
+      <c r="J1272">
+        <v>0</v>
+      </c>
+      <c r="K1272" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1273" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1273" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1273">
+        <v>4959</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1273" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1273" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1273" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1273" s="1">
+        <v>46146.674074074072</v>
+      </c>
+      <c r="J1273">
+        <v>0</v>
+      </c>
+      <c r="K1273" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1274" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1274" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1274">
+        <v>876</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1274" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1274" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1274">
+        <v>0</v>
+      </c>
+      <c r="I1274" s="1">
+        <v>46146.674768518518</v>
+      </c>
+      <c r="J1274">
+        <v>0</v>
+      </c>
+      <c r="K1274" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1275" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1275" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1275">
+        <v>3261</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1275" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1275" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1275" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1275" s="1">
+        <v>46146.675462962965</v>
+      </c>
+      <c r="J1275">
+        <v>0</v>
+      </c>
+      <c r="K1275" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1276" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1276" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1276">
+        <v>977</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1276" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1276" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1276" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1276" s="1">
+        <v>46146.675462962965</v>
+      </c>
+      <c r="J1276">
+        <v>0</v>
+      </c>
+      <c r="K1276" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1277" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1277" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1277">
+        <v>4888</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1277" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1277" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1277" s="1">
+        <v>46146.676157407404</v>
+      </c>
+      <c r="J1277">
+        <v>0</v>
+      </c>
+      <c r="K1277" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1278" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1278" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1278">
+        <v>888</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1278" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1278" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1278" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1278" s="1">
+        <v>46146.676851851851</v>
+      </c>
+      <c r="J1278">
+        <v>0</v>
+      </c>
+      <c r="K1278" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1279" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1279" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1279">
+        <v>871</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1279" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1279" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1279" s="1">
+        <v>46146.676851851851</v>
+      </c>
+      <c r="J1279">
+        <v>0</v>
+      </c>
+      <c r="K1279" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1280" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1280" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1280">
+        <v>873</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1280" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1280" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1280" s="2">
+        <v>4.363425925925926E-3</v>
+      </c>
+      <c r="I1280" s="1">
+        <v>46146.677546296298</v>
+      </c>
+      <c r="J1280">
+        <v>0</v>
+      </c>
+      <c r="K1280" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1281" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1281" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1281">
+        <v>5097</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1281" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1281" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1281" s="1">
+        <v>46146.678240740737</v>
+      </c>
+      <c r="J1281">
+        <v>0</v>
+      </c>
+      <c r="K1281" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1282" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1282" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1282">
+        <v>2800</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1282" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1282" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1282" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1282" s="1">
+        <v>46146.678240740737</v>
+      </c>
+      <c r="J1282">
+        <v>0</v>
+      </c>
+      <c r="K1282" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1283" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1283" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1283">
+        <v>891</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1283" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1283" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1283" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1283" s="1">
+        <v>46146.678935185184</v>
+      </c>
+      <c r="J1283">
+        <v>0</v>
+      </c>
+      <c r="K1283" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1284" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1284" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1284">
+        <v>898</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1284" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1284" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1284" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1284" s="1">
+        <v>46146.679629629631</v>
+      </c>
+      <c r="J1284">
+        <v>0</v>
+      </c>
+      <c r="K1284" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1285" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1285" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1285">
+        <v>905</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1285" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1285" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1285" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1285" s="1">
+        <v>46146.679629629631</v>
+      </c>
+      <c r="J1285">
+        <v>0</v>
+      </c>
+      <c r="K1285" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1286" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1286" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1286">
+        <v>894</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1286" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1286" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1286" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1286" s="1">
+        <v>46146.680324074077</v>
+      </c>
+      <c r="J1286">
+        <v>0</v>
+      </c>
+      <c r="K1286" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1287" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1287" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1287">
+        <v>896</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1287" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1287" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1287" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1287" s="1">
+        <v>46146.681018518517</v>
+      </c>
+      <c r="J1287">
+        <v>0</v>
+      </c>
+      <c r="K1287" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1288" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1288" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1288">
+        <v>3759</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1288" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1288" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1288" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1288" s="1">
+        <v>46146.681712962964</v>
+      </c>
+      <c r="J1288">
+        <v>0</v>
+      </c>
+      <c r="K1288" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1289" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1289" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1289">
+        <v>901</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1289" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1289" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1289" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1289" s="1">
+        <v>46146.681712962964</v>
+      </c>
+      <c r="J1289">
+        <v>0</v>
+      </c>
+      <c r="K1289" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1290" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1290" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1290">
+        <v>972</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1290" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1290" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1290" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1290" s="1">
+        <v>46146.68240740741</v>
+      </c>
+      <c r="J1290">
+        <v>0</v>
+      </c>
+      <c r="K1290" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1291" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1291" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1291">
+        <v>2808</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1291" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1291" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1291" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1291" s="1">
+        <v>46146.68310185185</v>
+      </c>
+      <c r="J1291">
+        <v>0</v>
+      </c>
+      <c r="K1291" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1292" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1292" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1292">
+        <v>5099</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1292" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1292" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1292" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1292" s="1">
+        <v>46146.68310185185</v>
+      </c>
+      <c r="J1292">
+        <v>0</v>
+      </c>
+      <c r="K1292" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1293" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1293" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1293">
+        <v>975</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1293" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1293" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1293" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1293" s="1">
+        <v>46146.683796296296</v>
+      </c>
+      <c r="J1293">
+        <v>0</v>
+      </c>
+      <c r="K1293" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1294" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1294" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1294">
+        <v>2806</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1294" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1294" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1294" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1294" s="1">
+        <v>46146.684490740743</v>
+      </c>
+      <c r="J1294">
+        <v>0</v>
+      </c>
+      <c r="K1294" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1295" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1295" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1295">
+        <v>3833</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1295" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1295" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1295" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1295" s="1">
+        <v>46146.684490740743</v>
+      </c>
+      <c r="J1295">
+        <v>0</v>
+      </c>
+      <c r="K1295" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1296" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1296" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1296">
+        <v>5098</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1296" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1296" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1296" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1296" s="1">
+        <v>46146.685185185182</v>
+      </c>
+      <c r="J1296">
+        <v>0</v>
+      </c>
+      <c r="K1296" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1297" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H1297" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mission Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC12B27E-DAA0-4D42-BAD8-F6E0F669D628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A958571-6FC4-4DEE-8739-2D4966A73262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -778,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K5929"/>
+  <dimension ref="A1:K5929"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -793,39 +793,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>35</v>
       </c>
@@ -854,7 +854,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>35</v>
       </c>
@@ -883,7 +883,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>35</v>
       </c>
@@ -970,7 +970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>35</v>
       </c>
@@ -999,7 +999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>35</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>35</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>35</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>35</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>35</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>35</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>35</v>
       </c>
@@ -33406,7 +33406,7 @@
         <v>46118.797337962962</v>
       </c>
       <c r="J1206">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1206" t="s">
         <v>11</v>
@@ -33435,7 +33435,7 @@
         <v>46118.797337962962</v>
       </c>
       <c r="J1207">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1207" t="s">
         <v>11</v>
@@ -33493,7 +33493,7 @@
         <v>46118.798726851855</v>
       </c>
       <c r="J1209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1209" t="s">
         <v>11</v>
@@ -33551,7 +33551,7 @@
         <v>46118.799421296295</v>
       </c>
       <c r="J1211">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1211" t="s">
         <v>11</v>
@@ -33580,7 +33580,7 @@
         <v>46118.799421296295</v>
       </c>
       <c r="J1212">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1212" t="s">
         <v>11</v>
@@ -33609,7 +33609,7 @@
         <v>46118.800115740742</v>
       </c>
       <c r="J1213">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1213" t="s">
         <v>11</v>
@@ -33870,7 +33870,7 @@
         <v>46118.804282407407</v>
       </c>
       <c r="J1222">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1222" t="s">
         <v>11</v>
@@ -33928,7 +33928,7 @@
         <v>46118.804976851854</v>
       </c>
       <c r="J1224">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1224" t="s">
         <v>11</v>
@@ -33986,7 +33986,7 @@
         <v>46118.805671296293</v>
       </c>
       <c r="J1226">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1226" t="s">
         <v>11</v>
@@ -34015,7 +34015,7 @@
         <v>46118.80636574074</v>
       </c>
       <c r="J1227">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1227" t="s">
         <v>11</v>
@@ -34102,7 +34102,7 @@
         <v>46118.807754629626</v>
       </c>
       <c r="J1230">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1230" t="s">
         <v>11</v>
@@ -34225,7 +34225,7 @@
         <v>46118.80914351852</v>
       </c>
       <c r="J1235">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1235" t="s">
         <v>11</v>
@@ -34457,7 +34457,7 @@
         <v>46118.812615740739</v>
       </c>
       <c r="J1243">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1243" t="s">
         <v>11</v>
@@ -34515,7 +34515,7 @@
         <v>46118.813310185185</v>
       </c>
       <c r="J1245">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1245" t="s">
         <v>11</v>
@@ -34544,7 +34544,7 @@
         <v>46118.814004629632</v>
       </c>
       <c r="J1246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1246" t="s">
         <v>11</v>
@@ -34573,7 +34573,7 @@
         <v>46118.814004629632</v>
       </c>
       <c r="J1247">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1247" t="s">
         <v>11</v>
@@ -35006,10 +35006,10 @@
         <v>18</v>
       </c>
       <c r="G1263" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1263" s="2">
-        <v>0</v>
+        <v>4.1666666666666666E-3</v>
       </c>
       <c r="I1263" s="1">
         <v>46146.669907407406</v>
@@ -35245,10 +35245,10 @@
         <v>18</v>
       </c>
       <c r="G1272" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1272" s="2">
-        <v>0</v>
+        <v>5.0694444444444441E-3</v>
       </c>
       <c r="I1272" s="1">
         <v>46146.674074074072</v>
@@ -35361,10 +35361,10 @@
         <v>18</v>
       </c>
       <c r="G1276" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1276" s="2">
-        <v>0</v>
+        <v>5.7986111111111112E-3</v>
       </c>
       <c r="I1276" s="1">
         <v>46146.675462962965</v>
@@ -35419,10 +35419,10 @@
         <v>18</v>
       </c>
       <c r="G1278" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1278" s="2">
-        <v>0</v>
+        <v>4.7569444444444447E-3</v>
       </c>
       <c r="I1278" s="1">
         <v>46146.676851851851</v>
@@ -35535,10 +35535,10 @@
         <v>18</v>
       </c>
       <c r="G1282" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1282" s="2">
-        <v>0</v>
+        <v>4.9768518518518521E-3</v>
       </c>
       <c r="I1282" s="1">
         <v>46146.678240740737</v>
@@ -35912,10 +35912,10 @@
         <v>18</v>
       </c>
       <c r="G1295" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1295" s="2">
-        <v>0</v>
+        <v>5.4282407407407404E-3</v>
       </c>
       <c r="I1295" s="1">
         <v>46146.684490740743</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mission Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C391985-44F5-42E9-B46A-893BEEC34F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F87D14-3794-413D-9AD4-7A5D60DFD76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -34696,7 +34696,7 @@
         <v>46146.687152777777</v>
       </c>
       <c r="J1252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1252" t="s">
         <v>11</v>
@@ -34716,16 +34716,16 @@
         <v>18</v>
       </c>
       <c r="G1253" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1253" s="2">
-        <v>0</v>
+        <v>5.3125000000000004E-3</v>
       </c>
       <c r="I1253" s="1">
         <v>46146.687847222223</v>
       </c>
       <c r="J1253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1253" t="s">
         <v>11</v>
@@ -34783,7 +34783,7 @@
         <v>46146.68854166667</v>
       </c>
       <c r="J1255">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1255" t="s">
         <v>11</v>
@@ -34841,7 +34841,7 @@
         <v>46146.689930555556</v>
       </c>
       <c r="J1257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1257" t="s">
         <v>11</v>
@@ -34870,7 +34870,7 @@
         <v>46146.689930555556</v>
       </c>
       <c r="J1258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1258" t="s">
         <v>11</v>
@@ -34899,7 +34899,7 @@
         <v>46146.690625000003</v>
       </c>
       <c r="J1259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1259" t="s">
         <v>11</v>
@@ -34957,7 +34957,7 @@
         <v>46146.66851851852</v>
       </c>
       <c r="J1261">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1261" t="s">
         <v>11</v>
@@ -34986,7 +34986,7 @@
         <v>46146.669212962966</v>
       </c>
       <c r="J1262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1262" t="s">
         <v>11</v>
@@ -35174,7 +35174,7 @@
         <v>46146.671990740739</v>
       </c>
       <c r="J1270">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1270" t="s">
         <v>11</v>
@@ -35232,7 +35232,7 @@
         <v>46146.673379629632</v>
       </c>
       <c r="J1272">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1272" t="s">
         <v>11</v>
@@ -35290,7 +35290,7 @@
         <v>46146.674074074072</v>
       </c>
       <c r="J1274">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1274" t="s">
         <v>11</v>
@@ -35319,7 +35319,7 @@
         <v>46146.674768518518</v>
       </c>
       <c r="J1275">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1275" t="s">
         <v>11</v>
@@ -35406,7 +35406,7 @@
         <v>46146.676157407404</v>
       </c>
       <c r="J1278">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1278" t="s">
         <v>11</v>
@@ -35464,7 +35464,7 @@
         <v>46146.676851851851</v>
       </c>
       <c r="J1280">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1280" t="s">
         <v>11</v>
@@ -35522,7 +35522,7 @@
         <v>46146.678240740737</v>
       </c>
       <c r="J1282">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1282" t="s">
         <v>11</v>
@@ -35600,16 +35600,16 @@
         <v>18</v>
       </c>
       <c r="G1285" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1285" s="2">
-        <v>0</v>
+        <v>4.9652777777777777E-3</v>
       </c>
       <c r="I1285" s="1">
         <v>46146.679629629631</v>
       </c>
       <c r="J1285">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1285" t="s">
         <v>11</v>
@@ -35725,7 +35725,7 @@
         <v>46146.681712962964</v>
       </c>
       <c r="J1289">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1289" t="s">
         <v>11</v>
@@ -35754,7 +35754,7 @@
         <v>46146.681712962964</v>
       </c>
       <c r="J1290">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1290" t="s">
         <v>11</v>
@@ -35783,7 +35783,7 @@
         <v>46146.68240740741</v>
       </c>
       <c r="J1291">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1291" t="s">
         <v>11</v>
@@ -35812,7 +35812,7 @@
         <v>46146.68310185185</v>
       </c>
       <c r="J1292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1292" t="s">
         <v>11</v>
@@ -35841,7 +35841,7 @@
         <v>46146.68310185185</v>
       </c>
       <c r="J1293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1293" t="s">
         <v>11</v>
@@ -35870,7 +35870,7 @@
         <v>46146.683796296296</v>
       </c>
       <c r="J1294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1294" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mission Wrecker- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mission-Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED920CDC-70B5-41F4-B792-7678B43EFA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4ECE40-D7E6-4D33-A686-F9CE30A856AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36458,7 +36458,7 @@
         <v>46176.473611111112</v>
       </c>
       <c r="J1307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1307" t="s">
         <v>11</v>
@@ -36516,7 +36516,7 @@
         <v>46176.474305555559</v>
       </c>
       <c r="J1309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1309" t="s">
         <v>11</v>
@@ -36574,7 +36574,7 @@
         <v>46176.474999999999</v>
       </c>
       <c r="J1311">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1311" t="s">
         <v>11</v>
@@ -36603,7 +36603,7 @@
         <v>46176.474999999999</v>
       </c>
       <c r="J1312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1312" t="s">
         <v>11</v>
@@ -36632,7 +36632,7 @@
         <v>46176.475694444445</v>
       </c>
       <c r="J1313">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1313" t="s">
         <v>11</v>
@@ -36661,7 +36661,7 @@
         <v>46176.475694444445</v>
       </c>
       <c r="J1314">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1314" t="s">
         <v>11</v>
@@ -36690,7 +36690,7 @@
         <v>46176.475694444445</v>
       </c>
       <c r="J1315">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1315" t="s">
         <v>11</v>
@@ -36815,7 +36815,7 @@
         <v>46176.459837962961</v>
       </c>
       <c r="J1320">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1320" t="s">
         <v>11</v>
@@ -36844,7 +36844,7 @@
         <v>46176.459837962961</v>
       </c>
       <c r="J1321">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1321" t="s">
         <v>11</v>
@@ -36931,7 +36931,7 @@
         <v>46176.461226851854</v>
       </c>
       <c r="J1324">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1324" t="s">
         <v>11</v>
@@ -36960,7 +36960,7 @@
         <v>46176.461226851854</v>
       </c>
       <c r="J1325">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1325" t="s">
         <v>11</v>
@@ -37018,7 +37018,7 @@
         <v>46176.461921296293</v>
       </c>
       <c r="J1327">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1327" t="s">
         <v>11</v>
@@ -37047,7 +37047,7 @@
         <v>46176.46261574074</v>
       </c>
       <c r="J1328">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1328" t="s">
         <v>11</v>
@@ -37076,7 +37076,7 @@
         <v>46176.46261574074</v>
       </c>
       <c r="J1329">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1329" t="s">
         <v>11</v>
@@ -37105,7 +37105,7 @@
         <v>46176.46261574074</v>
       </c>
       <c r="J1330">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1330" t="s">
         <v>11</v>
@@ -37163,7 +37163,7 @@
         <v>46176.463310185187</v>
       </c>
       <c r="J1332">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1332" t="s">
         <v>11</v>
@@ -37279,7 +37279,7 @@
         <v>46176.464699074073</v>
       </c>
       <c r="J1336">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1336" t="s">
         <v>11</v>
@@ -37308,7 +37308,7 @@
         <v>46176.464699074073</v>
       </c>
       <c r="J1337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1337" t="s">
         <v>11</v>
@@ -37337,7 +37337,7 @@
         <v>46176.46539351852</v>
       </c>
       <c r="J1338">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1338" t="s">
         <v>11</v>
@@ -37366,7 +37366,7 @@
         <v>46176.46539351852</v>
       </c>
       <c r="J1339">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1339" t="s">
         <v>11</v>
@@ -37395,7 +37395,7 @@
         <v>46176.46539351852</v>
       </c>
       <c r="J1340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1340" t="s">
         <v>11</v>
@@ -37424,7 +37424,7 @@
         <v>46176.466087962966</v>
       </c>
       <c r="J1341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1341" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mission-Wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEA65CFD-14F7-4213-9D26-6261233FF2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ABDF5D1-1157-4C7C-B984-A3678BB4A9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -98,10 +98,16 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
+    <t>Driver Health</t>
+  </si>
+  <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -116,40 +122,34 @@
     <t>DNU-Driver Health</t>
   </si>
   <si>
-    <t>Safe RR Crossing</t>
-  </si>
-  <si>
-    <t>3 points of contact</t>
-  </si>
-  <si>
-    <t>In Cab Distractions</t>
+    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Micro-Learn Speed</t>
   </si>
   <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
     <t>Micro-Learn Space Mangement</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>Fire Extinguisher Training for CDL</t>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
-    <t>Camera Event Management Orientation for Drivers</t>
+    <t>3 points of contact</t>
   </si>
   <si>
     <t>Micro-Learn Safe Following Distance</t>
   </si>
   <si>
     <t>Hazcom for CDL Drivers</t>
+  </si>
+  <si>
+    <t>Safe RR Crossing</t>
+  </si>
+  <si>
+    <t>In Cab Distractions</t>
   </si>
   <si>
     <t>Mission Wrecker Service - Heavy Duty Towing</t>
@@ -781,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -839,7 +839,7 @@
         <v>38</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -868,7 +868,7 @@
         <v>39</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -897,7 +897,7 @@
         <v>40</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -926,7 +926,7 @@
         <v>41</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -955,7 +955,7 @@
         <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -1013,7 +1013,7 @@
         <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -1042,7 +1042,7 @@
         <v>45</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>46</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -1100,7 +1100,7 @@
         <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -1129,7 +1129,7 @@
         <v>47</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -1158,7 +1158,7 @@
         <v>48</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -1187,7 +1187,7 @@
         <v>49</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -1216,7 +1216,7 @@
         <v>50</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1245,7 +1245,7 @@
         <v>51</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>12</v>
@@ -1269,7 +1269,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="1"/>
       <c r="M17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
@@ -1283,7 +1283,7 @@
         <v>52</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1312,7 +1312,7 @@
         <v>53</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>14</v>
@@ -1336,7 +1336,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="1"/>
       <c r="M20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
@@ -1350,7 +1350,7 @@
         <v>54</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1379,7 +1379,7 @@
         <v>55</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -1408,7 +1408,7 @@
         <v>56</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1437,7 +1437,7 @@
         <v>57</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1466,7 +1466,7 @@
         <v>58</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>12</v>
@@ -1490,7 +1490,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1504,7 +1504,7 @@
         <v>59</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1533,7 +1533,7 @@
         <v>60</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1562,7 +1562,7 @@
         <v>61</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1591,7 +1591,7 @@
         <v>62</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1620,7 +1620,7 @@
         <v>63</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1649,7 +1649,7 @@
         <v>64</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1678,7 +1678,7 @@
         <v>65</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1707,7 +1707,7 @@
         <v>66</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1736,7 +1736,7 @@
         <v>67</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1765,7 +1765,7 @@
         <v>68</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1794,7 +1794,7 @@
         <v>69</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1823,7 +1823,7 @@
         <v>70</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1852,7 +1852,7 @@
         <v>71</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1881,7 +1881,7 @@
         <v>72</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1910,7 +1910,7 @@
         <v>73</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1939,7 +1939,7 @@
         <v>74</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1968,7 +1968,7 @@
         <v>75</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1997,7 +1997,7 @@
         <v>76</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -2026,7 +2026,7 @@
         <v>77</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -2055,7 +2055,7 @@
         <v>78</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -2084,7 +2084,7 @@
         <v>79</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -2113,7 +2113,7 @@
         <v>80</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -2142,7 +2142,7 @@
         <v>81</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -2171,7 +2171,7 @@
         <v>82</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -2200,7 +2200,7 @@
         <v>83</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -2229,7 +2229,7 @@
         <v>84</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -2258,7 +2258,7 @@
         <v>85</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -2287,7 +2287,7 @@
         <v>86</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2316,7 +2316,7 @@
         <v>87</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2345,7 +2345,7 @@
         <v>88</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2374,7 +2374,7 @@
         <v>89</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2456,7 +2456,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="1"/>
       <c r="M60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
@@ -2552,7 +2552,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="1"/>
       <c r="M64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
@@ -2619,7 +2619,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="1"/>
       <c r="M67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
@@ -2686,7 +2686,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="1"/>
       <c r="M70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
@@ -2753,7 +2753,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="1"/>
       <c r="M73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
@@ -2820,7 +2820,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="1"/>
       <c r="M76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
@@ -2916,7 +2916,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="1"/>
       <c r="M80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
@@ -2983,7 +2983,7 @@
       <c r="J83" s="2"/>
       <c r="K83" s="1"/>
       <c r="M83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
@@ -3050,7 +3050,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="1"/>
       <c r="M86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
@@ -3088,7 +3088,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="1"/>
       <c r="M88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
@@ -3126,7 +3126,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="1"/>
       <c r="M90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
@@ -3164,7 +3164,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="1"/>
       <c r="M92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
@@ -3202,7 +3202,7 @@
       <c r="J94" s="2"/>
       <c r="K94" s="1"/>
       <c r="M94" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
@@ -3269,7 +3269,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="1"/>
       <c r="M97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
@@ -3568,7 +3568,7 @@
       <c r="J108" s="2"/>
       <c r="K108" s="1"/>
       <c r="M108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
@@ -3664,7 +3664,7 @@
       <c r="J112" s="2"/>
       <c r="K112" s="1"/>
       <c r="M112" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
@@ -3702,7 +3702,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
       <c r="M114" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
@@ -3856,7 +3856,7 @@
       <c r="J120" s="2"/>
       <c r="K120" s="1"/>
       <c r="M120" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
@@ -3923,7 +3923,7 @@
       <c r="J123" s="2"/>
       <c r="K123" s="1"/>
       <c r="M123" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
@@ -4048,7 +4048,7 @@
       <c r="J128" s="2"/>
       <c r="K128" s="1"/>
       <c r="M128" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
@@ -4144,7 +4144,7 @@
       <c r="J132" s="2"/>
       <c r="K132" s="1"/>
       <c r="M132" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
@@ -4327,7 +4327,7 @@
       <c r="J139" s="2"/>
       <c r="K139" s="1"/>
       <c r="M139" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
@@ -4510,7 +4510,7 @@
       <c r="J146" s="2"/>
       <c r="K146" s="1"/>
       <c r="M146" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
@@ -4577,7 +4577,7 @@
       <c r="J149" s="2"/>
       <c r="K149" s="1"/>
       <c r="M149" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
@@ -4818,7 +4818,7 @@
       <c r="J158" s="2"/>
       <c r="K158" s="1"/>
       <c r="M158" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
@@ -4972,7 +4972,7 @@
       <c r="J164" s="2"/>
       <c r="K164" s="1"/>
       <c r="M164" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
@@ -5039,7 +5039,7 @@
       <c r="J167" s="2"/>
       <c r="K167" s="1"/>
       <c r="M167" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
@@ -5164,7 +5164,7 @@
       <c r="J172" s="2"/>
       <c r="K172" s="1"/>
       <c r="M172" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
@@ -5231,7 +5231,7 @@
       <c r="J175" s="2"/>
       <c r="K175" s="1"/>
       <c r="M175" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
@@ -5298,7 +5298,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
       <c r="M178" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
@@ -5452,7 +5452,7 @@
       <c r="J184" s="2"/>
       <c r="K184" s="1"/>
       <c r="M184" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="4:13" x14ac:dyDescent="0.3">
@@ -5519,7 +5519,7 @@
       <c r="J187" s="2"/>
       <c r="K187" s="1"/>
       <c r="M187" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
@@ -5702,7 +5702,7 @@
       <c r="J194" s="2"/>
       <c r="K194" s="1"/>
       <c r="M194" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
@@ -5740,7 +5740,7 @@
       <c r="J196" s="2"/>
       <c r="K196" s="1"/>
       <c r="M196" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="4:13" x14ac:dyDescent="0.3">
@@ -6039,7 +6039,7 @@
       <c r="J207" s="2"/>
       <c r="K207" s="1"/>
       <c r="M207" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
@@ -6773,7 +6773,7 @@
       <c r="J233" s="2"/>
       <c r="K233" s="1"/>
       <c r="M233" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="234" spans="4:13" x14ac:dyDescent="0.3">
@@ -7043,7 +7043,7 @@
       <c r="J243" s="2"/>
       <c r="K243" s="1"/>
       <c r="M243" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="244" spans="4:13" x14ac:dyDescent="0.3">
@@ -7226,7 +7226,7 @@
       <c r="J250" s="2"/>
       <c r="K250" s="1"/>
       <c r="M250" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
@@ -7554,7 +7554,7 @@
       <c r="J262" s="2"/>
       <c r="K262" s="1"/>
       <c r="M262" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="263" spans="4:13" x14ac:dyDescent="0.3">
@@ -7679,7 +7679,7 @@
       <c r="J267" s="2"/>
       <c r="K267" s="1"/>
       <c r="M267" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="268" spans="4:13" x14ac:dyDescent="0.3">
@@ -8007,7 +8007,7 @@
       <c r="J279" s="2"/>
       <c r="K279" s="1"/>
       <c r="M279" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="280" spans="4:13" x14ac:dyDescent="0.3">
@@ -8340,7 +8340,7 @@
         <v>39</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>13</v>
@@ -8369,7 +8369,7 @@
         <v>40</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>13</v>
@@ -8398,7 +8398,7 @@
         <v>41</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>10</v>
@@ -8427,7 +8427,7 @@
         <v>42</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -8456,7 +8456,7 @@
         <v>43</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>10</v>
@@ -8485,7 +8485,7 @@
         <v>44</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8514,7 +8514,7 @@
         <v>45</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>10</v>
@@ -8543,7 +8543,7 @@
         <v>46</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>10</v>
@@ -8572,7 +8572,7 @@
         <v>47</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>13</v>
@@ -8601,7 +8601,7 @@
         <v>47</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>13</v>
@@ -8630,7 +8630,7 @@
         <v>48</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>13</v>
@@ -8659,7 +8659,7 @@
         <v>49</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -8688,7 +8688,7 @@
         <v>50</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>10</v>
@@ -8717,7 +8717,7 @@
         <v>51</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>13</v>
@@ -8746,7 +8746,7 @@
         <v>52</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>13</v>
@@ -8775,7 +8775,7 @@
         <v>53</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -8804,7 +8804,7 @@
         <v>55</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>10</v>
@@ -8833,7 +8833,7 @@
         <v>56</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>13</v>
@@ -8862,7 +8862,7 @@
         <v>57</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>13</v>
@@ -8891,7 +8891,7 @@
         <v>58</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>13</v>
@@ -8920,7 +8920,7 @@
         <v>59</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>10</v>
@@ -8949,7 +8949,7 @@
         <v>60</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>12</v>
@@ -8973,7 +8973,7 @@
       <c r="J313" s="2"/>
       <c r="K313" s="1"/>
       <c r="M313" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="314" spans="4:13" x14ac:dyDescent="0.3">
@@ -8987,7 +8987,7 @@
         <v>61</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>13</v>
@@ -9016,7 +9016,7 @@
         <v>62</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>10</v>
@@ -9045,7 +9045,7 @@
         <v>63</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>10</v>
@@ -9074,7 +9074,7 @@
         <v>64</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>10</v>
@@ -9103,7 +9103,7 @@
         <v>65</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>10</v>
@@ -9132,7 +9132,7 @@
         <v>66</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>10</v>
@@ -9161,7 +9161,7 @@
         <v>91</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>12</v>
@@ -9185,7 +9185,7 @@
       <c r="J321" s="2"/>
       <c r="K321" s="1"/>
       <c r="M321" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="322" spans="4:13" x14ac:dyDescent="0.3">
@@ -9199,7 +9199,7 @@
         <v>69</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>10</v>
@@ -9228,7 +9228,7 @@
         <v>70</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>13</v>
@@ -9257,7 +9257,7 @@
         <v>71</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>10</v>
@@ -9286,7 +9286,7 @@
         <v>72</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>13</v>
@@ -9315,7 +9315,7 @@
         <v>73</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>13</v>
@@ -9344,7 +9344,7 @@
         <v>74</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>13</v>
@@ -9373,7 +9373,7 @@
         <v>75</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>10</v>
@@ -9402,7 +9402,7 @@
         <v>76</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>13</v>
@@ -9431,7 +9431,7 @@
         <v>92</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>13</v>
@@ -9460,7 +9460,7 @@
         <v>77</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>13</v>
@@ -9489,7 +9489,7 @@
         <v>78</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>79</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>13</v>
@@ -9547,7 +9547,7 @@
         <v>80</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>13</v>
@@ -9576,7 +9576,7 @@
         <v>81</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>13</v>
@@ -9605,7 +9605,7 @@
         <v>82</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>13</v>
@@ -9634,7 +9634,7 @@
         <v>83</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>10</v>
@@ -9663,7 +9663,7 @@
         <v>84</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>13</v>
@@ -9692,7 +9692,7 @@
         <v>85</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -9721,7 +9721,7 @@
         <v>86</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>13</v>
@@ -9750,7 +9750,7 @@
         <v>87</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>13</v>
@@ -9779,7 +9779,7 @@
         <v>88</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>13</v>
@@ -9808,7 +9808,7 @@
         <v>89</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -9861,7 +9861,7 @@
       <c r="J345" s="2"/>
       <c r="K345" s="1"/>
       <c r="M345" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="346" spans="4:13" x14ac:dyDescent="0.3">
@@ -10363,7 +10363,7 @@
       <c r="J363" s="2"/>
       <c r="K363" s="1"/>
       <c r="M363" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="364" spans="4:13" x14ac:dyDescent="0.3">
@@ -10691,7 +10691,7 @@
       <c r="J375" s="2"/>
       <c r="K375" s="1"/>
       <c r="M375" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="376" spans="4:13" x14ac:dyDescent="0.3">
@@ -11193,7 +11193,7 @@
       <c r="J393" s="2"/>
       <c r="K393" s="1"/>
       <c r="M393" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="394" spans="4:13" x14ac:dyDescent="0.3">
@@ -11405,7 +11405,7 @@
       <c r="J401" s="2"/>
       <c r="K401" s="1"/>
       <c r="M401" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="402" spans="4:13" x14ac:dyDescent="0.3">
@@ -11559,7 +11559,7 @@
       <c r="J407" s="2"/>
       <c r="K407" s="1"/>
       <c r="M407" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="408" spans="4:13" x14ac:dyDescent="0.3">
@@ -11684,7 +11684,7 @@
       <c r="J412" s="2"/>
       <c r="K412" s="1"/>
       <c r="M412" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="413" spans="4:13" x14ac:dyDescent="0.3">
@@ -12128,7 +12128,7 @@
       <c r="J428" s="2"/>
       <c r="K428" s="1"/>
       <c r="M428" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="429" spans="4:13" x14ac:dyDescent="0.3">
@@ -12311,7 +12311,7 @@
       <c r="J435" s="2"/>
       <c r="K435" s="1"/>
       <c r="M435" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="436" spans="4:13" x14ac:dyDescent="0.3">
@@ -12407,7 +12407,7 @@
       <c r="J439" s="2"/>
       <c r="K439" s="1"/>
       <c r="M439" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="440" spans="4:13" x14ac:dyDescent="0.3">
@@ -13025,7 +13025,7 @@
       <c r="J461" s="2"/>
       <c r="K461" s="1"/>
       <c r="M461" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="462" spans="4:13" x14ac:dyDescent="0.3">
@@ -13121,7 +13121,7 @@
       <c r="J465" s="2"/>
       <c r="K465" s="1"/>
       <c r="M465" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="466" spans="4:13" x14ac:dyDescent="0.3">
@@ -13159,7 +13159,7 @@
       <c r="J467" s="2"/>
       <c r="K467" s="1"/>
       <c r="M467" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="468" spans="4:13" x14ac:dyDescent="0.3">
@@ -13603,7 +13603,7 @@
       <c r="J483" s="2"/>
       <c r="K483" s="1"/>
       <c r="M483" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="484" spans="4:13" x14ac:dyDescent="0.3">
@@ -13960,7 +13960,7 @@
       <c r="J496" s="2"/>
       <c r="K496" s="1"/>
       <c r="M496" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="497" spans="4:13" x14ac:dyDescent="0.3">
@@ -13974,7 +13974,7 @@
         <v>40</v>
       </c>
       <c r="H497" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I497" s="1" t="s">
         <v>13</v>
@@ -14003,7 +14003,7 @@
         <v>42</v>
       </c>
       <c r="H498" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I498" s="1" t="s">
         <v>10</v>
@@ -14032,7 +14032,7 @@
         <v>95</v>
       </c>
       <c r="H499" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I499" s="1" t="s">
         <v>12</v>
@@ -14056,7 +14056,7 @@
       <c r="J500" s="2"/>
       <c r="K500" s="1"/>
       <c r="M500" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="501" spans="4:13" x14ac:dyDescent="0.3">
@@ -14070,7 +14070,7 @@
         <v>43</v>
       </c>
       <c r="H501" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I501" s="1" t="s">
         <v>13</v>
@@ -14099,7 +14099,7 @@
         <v>44</v>
       </c>
       <c r="H502" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I502" s="1" t="s">
         <v>10</v>
@@ -14128,7 +14128,7 @@
         <v>96</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I503" s="1" t="s">
         <v>14</v>
@@ -14152,7 +14152,7 @@
       <c r="J504" s="2"/>
       <c r="K504" s="1"/>
       <c r="M504" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="505" spans="4:13" x14ac:dyDescent="0.3">
@@ -14166,7 +14166,7 @@
         <v>45</v>
       </c>
       <c r="H505" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I505" s="1" t="s">
         <v>10</v>
@@ -14195,7 +14195,7 @@
         <v>46</v>
       </c>
       <c r="H506" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I506" s="1" t="s">
         <v>13</v>
@@ -14224,7 +14224,7 @@
         <v>47</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I507" s="1" t="s">
         <v>13</v>
@@ -14253,7 +14253,7 @@
         <v>49</v>
       </c>
       <c r="H508" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I508" s="1" t="s">
         <v>10</v>
@@ -14282,7 +14282,7 @@
         <v>50</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I509" s="1" t="s">
         <v>10</v>
@@ -14311,7 +14311,7 @@
         <v>52</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I510" s="1" t="s">
         <v>10</v>
@@ -14340,7 +14340,7 @@
         <v>53</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I511" s="1" t="s">
         <v>10</v>
@@ -14369,7 +14369,7 @@
         <v>55</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I512" s="1" t="s">
         <v>10</v>
@@ -14398,7 +14398,7 @@
         <v>56</v>
       </c>
       <c r="H513" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I513" s="1" t="s">
         <v>10</v>
@@ -14427,7 +14427,7 @@
         <v>97</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I514" s="1" t="s">
         <v>13</v>
@@ -14456,7 +14456,7 @@
         <v>57</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I515" s="1" t="s">
         <v>14</v>
@@ -14480,7 +14480,7 @@
       <c r="J516" s="2"/>
       <c r="K516" s="1"/>
       <c r="M516" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="517" spans="4:13" x14ac:dyDescent="0.3">
@@ -14494,7 +14494,7 @@
         <v>58</v>
       </c>
       <c r="H517" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I517" s="1" t="s">
         <v>10</v>
@@ -14523,7 +14523,7 @@
         <v>59</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I518" s="1" t="s">
         <v>10</v>
@@ -14552,7 +14552,7 @@
         <v>62</v>
       </c>
       <c r="H519" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I519" s="1" t="s">
         <v>10</v>
@@ -14581,7 +14581,7 @@
         <v>63</v>
       </c>
       <c r="H520" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I520" s="1" t="s">
         <v>10</v>
@@ -14610,7 +14610,7 @@
         <v>64</v>
       </c>
       <c r="H521" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I521" s="1" t="s">
         <v>13</v>
@@ -14639,7 +14639,7 @@
         <v>65</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I522" s="1" t="s">
         <v>10</v>
@@ -14668,7 +14668,7 @@
         <v>66</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I523" s="1" t="s">
         <v>10</v>
@@ -14697,7 +14697,7 @@
         <v>98</v>
       </c>
       <c r="H524" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I524" s="1" t="s">
         <v>13</v>
@@ -14726,7 +14726,7 @@
         <v>69</v>
       </c>
       <c r="H525" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I525" s="1" t="s">
         <v>10</v>
@@ -14755,7 +14755,7 @@
         <v>70</v>
       </c>
       <c r="H526" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I526" s="1" t="s">
         <v>13</v>
@@ -14784,7 +14784,7 @@
         <v>71</v>
       </c>
       <c r="H527" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I527" s="1" t="s">
         <v>10</v>
@@ -14813,7 +14813,7 @@
         <v>99</v>
       </c>
       <c r="H528" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I528" s="1" t="s">
         <v>10</v>
@@ -14842,7 +14842,7 @@
         <v>72</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I529" s="1" t="s">
         <v>13</v>
@@ -14871,7 +14871,7 @@
         <v>73</v>
       </c>
       <c r="H530" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I530" s="1" t="s">
         <v>13</v>
@@ -14900,7 +14900,7 @@
         <v>74</v>
       </c>
       <c r="H531" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I531" s="1" t="s">
         <v>13</v>
@@ -14929,7 +14929,7 @@
         <v>74</v>
       </c>
       <c r="H532" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I532" s="1" t="s">
         <v>13</v>
@@ -14958,7 +14958,7 @@
         <v>100</v>
       </c>
       <c r="H533" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I533" s="1" t="s">
         <v>12</v>
@@ -14982,7 +14982,7 @@
       <c r="J534" s="2"/>
       <c r="K534" s="1"/>
       <c r="M534" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="535" spans="4:13" x14ac:dyDescent="0.3">
@@ -14996,7 +14996,7 @@
         <v>75</v>
       </c>
       <c r="H535" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I535" s="1" t="s">
         <v>10</v>
@@ -15025,7 +15025,7 @@
         <v>76</v>
       </c>
       <c r="H536" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I536" s="1" t="s">
         <v>13</v>
@@ -15054,7 +15054,7 @@
         <v>101</v>
       </c>
       <c r="H537" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I537" s="1" t="s">
         <v>13</v>
@@ -15083,7 +15083,7 @@
         <v>77</v>
       </c>
       <c r="H538" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I538" s="1" t="s">
         <v>13</v>
@@ -15112,7 +15112,7 @@
         <v>78</v>
       </c>
       <c r="H539" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I539" s="1" t="s">
         <v>10</v>
@@ -15141,7 +15141,7 @@
         <v>79</v>
       </c>
       <c r="H540" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I540" s="1" t="s">
         <v>13</v>
@@ -15170,7 +15170,7 @@
         <v>102</v>
       </c>
       <c r="H541" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I541" s="1" t="s">
         <v>10</v>
@@ -15199,7 +15199,7 @@
         <v>103</v>
       </c>
       <c r="H542" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I542" s="1" t="s">
         <v>10</v>
@@ -15228,7 +15228,7 @@
         <v>81</v>
       </c>
       <c r="H543" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I543" s="1" t="s">
         <v>13</v>
@@ -15257,7 +15257,7 @@
         <v>83</v>
       </c>
       <c r="H544" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I544" s="1" t="s">
         <v>13</v>
@@ -15286,7 +15286,7 @@
         <v>104</v>
       </c>
       <c r="H545" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I545" s="1" t="s">
         <v>13</v>
@@ -15315,7 +15315,7 @@
         <v>85</v>
       </c>
       <c r="H546" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I546" s="1" t="s">
         <v>10</v>
@@ -15344,7 +15344,7 @@
         <v>87</v>
       </c>
       <c r="H547" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I547" s="1" t="s">
         <v>13</v>
@@ -15373,7 +15373,7 @@
         <v>105</v>
       </c>
       <c r="H548" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I548" s="1" t="s">
         <v>10</v>
@@ -15402,7 +15402,7 @@
         <v>88</v>
       </c>
       <c r="H549" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I549" s="1" t="s">
         <v>13</v>
@@ -15431,7 +15431,7 @@
         <v>40</v>
       </c>
       <c r="H550" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I550" s="1" t="s">
         <v>13</v>
@@ -15460,7 +15460,7 @@
         <v>42</v>
       </c>
       <c r="H551" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I551" s="1" t="s">
         <v>13</v>
@@ -15489,7 +15489,7 @@
         <v>95</v>
       </c>
       <c r="H552" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I552" s="1" t="s">
         <v>13</v>
@@ -15518,7 +15518,7 @@
         <v>43</v>
       </c>
       <c r="H553" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I553" s="1" t="s">
         <v>13</v>
@@ -15547,7 +15547,7 @@
         <v>44</v>
       </c>
       <c r="H554" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I554" s="1" t="s">
         <v>13</v>
@@ -15576,7 +15576,7 @@
         <v>96</v>
       </c>
       <c r="H555" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I555" s="1" t="s">
         <v>13</v>
@@ -15605,7 +15605,7 @@
         <v>45</v>
       </c>
       <c r="H556" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I556" s="1" t="s">
         <v>13</v>
@@ -15634,7 +15634,7 @@
         <v>47</v>
       </c>
       <c r="H557" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I557" s="1" t="s">
         <v>13</v>
@@ -15663,7 +15663,7 @@
         <v>49</v>
       </c>
       <c r="H558" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I558" s="1" t="s">
         <v>10</v>
@@ -15692,7 +15692,7 @@
         <v>50</v>
       </c>
       <c r="H559" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I559" s="1" t="s">
         <v>10</v>
@@ -15721,7 +15721,7 @@
         <v>52</v>
       </c>
       <c r="H560" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I560" s="1" t="s">
         <v>10</v>
@@ -15750,7 +15750,7 @@
         <v>53</v>
       </c>
       <c r="H561" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I561" s="1" t="s">
         <v>12</v>
@@ -15774,7 +15774,7 @@
       <c r="J562" s="2"/>
       <c r="K562" s="1"/>
       <c r="M562" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="563" spans="4:13" x14ac:dyDescent="0.3">
@@ -15788,7 +15788,7 @@
         <v>55</v>
       </c>
       <c r="H563" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I563" s="1" t="s">
         <v>10</v>
@@ -15817,7 +15817,7 @@
         <v>56</v>
       </c>
       <c r="H564" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I564" s="1" t="s">
         <v>13</v>
@@ -15846,7 +15846,7 @@
         <v>97</v>
       </c>
       <c r="H565" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I565" s="1" t="s">
         <v>13</v>
@@ -15875,7 +15875,7 @@
         <v>57</v>
       </c>
       <c r="H566" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I566" s="1" t="s">
         <v>13</v>
@@ -15904,7 +15904,7 @@
         <v>58</v>
       </c>
       <c r="H567" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I567" s="1" t="s">
         <v>13</v>
@@ -15933,7 +15933,7 @@
         <v>59</v>
       </c>
       <c r="H568" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I568" s="1" t="s">
         <v>10</v>
@@ -15962,7 +15962,7 @@
         <v>62</v>
       </c>
       <c r="H569" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I569" s="1" t="s">
         <v>10</v>
@@ -15991,7 +15991,7 @@
         <v>63</v>
       </c>
       <c r="H570" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I570" s="1" t="s">
         <v>14</v>
@@ -16015,7 +16015,7 @@
       <c r="J571" s="2"/>
       <c r="K571" s="1"/>
       <c r="M571" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="572" spans="4:13" x14ac:dyDescent="0.3">
@@ -16029,7 +16029,7 @@
         <v>64</v>
       </c>
       <c r="H572" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I572" s="1" t="s">
         <v>13</v>
@@ -16058,7 +16058,7 @@
         <v>65</v>
       </c>
       <c r="H573" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I573" s="1" t="s">
         <v>10</v>
@@ -16087,7 +16087,7 @@
         <v>66</v>
       </c>
       <c r="H574" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I574" s="1" t="s">
         <v>10</v>
@@ -16116,7 +16116,7 @@
         <v>69</v>
       </c>
       <c r="H575" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I575" s="1" t="s">
         <v>10</v>
@@ -16145,7 +16145,7 @@
         <v>70</v>
       </c>
       <c r="H576" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I576" s="1" t="s">
         <v>13</v>
@@ -16174,7 +16174,7 @@
         <v>71</v>
       </c>
       <c r="H577" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I577" s="1" t="s">
         <v>13</v>
@@ -16203,7 +16203,7 @@
         <v>99</v>
       </c>
       <c r="H578" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I578" s="1" t="s">
         <v>10</v>
@@ -16232,7 +16232,7 @@
         <v>72</v>
       </c>
       <c r="H579" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I579" s="1" t="s">
         <v>13</v>
@@ -16261,7 +16261,7 @@
         <v>73</v>
       </c>
       <c r="H580" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I580" s="1" t="s">
         <v>13</v>
@@ -16290,7 +16290,7 @@
         <v>74</v>
       </c>
       <c r="H581" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I581" s="1" t="s">
         <v>13</v>
@@ -16319,7 +16319,7 @@
         <v>74</v>
       </c>
       <c r="H582" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I582" s="1" t="s">
         <v>13</v>
@@ -16348,7 +16348,7 @@
         <v>100</v>
       </c>
       <c r="H583" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I583" s="1" t="s">
         <v>13</v>
@@ -16377,7 +16377,7 @@
         <v>75</v>
       </c>
       <c r="H584" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I584" s="1" t="s">
         <v>13</v>
@@ -16406,7 +16406,7 @@
         <v>76</v>
       </c>
       <c r="H585" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I585" s="1" t="s">
         <v>13</v>
@@ -16435,7 +16435,7 @@
         <v>101</v>
       </c>
       <c r="H586" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I586" s="1" t="s">
         <v>13</v>
@@ -16464,7 +16464,7 @@
         <v>77</v>
       </c>
       <c r="H587" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I587" s="1" t="s">
         <v>13</v>
@@ -16493,7 +16493,7 @@
         <v>78</v>
       </c>
       <c r="H588" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I588" s="1" t="s">
         <v>13</v>
@@ -16522,7 +16522,7 @@
         <v>79</v>
       </c>
       <c r="H589" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I589" s="1" t="s">
         <v>13</v>
@@ -16551,7 +16551,7 @@
         <v>102</v>
       </c>
       <c r="H590" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I590" s="1" t="s">
         <v>13</v>
@@ -16580,7 +16580,7 @@
         <v>103</v>
       </c>
       <c r="H591" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I591" s="1" t="s">
         <v>13</v>
@@ -16609,7 +16609,7 @@
         <v>81</v>
       </c>
       <c r="H592" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I592" s="1" t="s">
         <v>13</v>
@@ -16638,7 +16638,7 @@
         <v>83</v>
       </c>
       <c r="H593" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I593" s="1" t="s">
         <v>13</v>
@@ -16667,7 +16667,7 @@
         <v>104</v>
       </c>
       <c r="H594" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I594" s="1" t="s">
         <v>13</v>
@@ -16696,7 +16696,7 @@
         <v>85</v>
       </c>
       <c r="H595" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I595" s="1" t="s">
         <v>12</v>
@@ -16720,7 +16720,7 @@
       <c r="J596" s="2"/>
       <c r="K596" s="1"/>
       <c r="M596" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="597" spans="4:13" x14ac:dyDescent="0.3">
@@ -16734,7 +16734,7 @@
         <v>87</v>
       </c>
       <c r="H597" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I597" s="1" t="s">
         <v>13</v>
@@ -16763,7 +16763,7 @@
         <v>105</v>
       </c>
       <c r="H598" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I598" s="1" t="s">
         <v>10</v>
@@ -16792,7 +16792,7 @@
         <v>88</v>
       </c>
       <c r="H599" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I599" s="1" t="s">
         <v>13</v>
@@ -16821,7 +16821,7 @@
         <v>106</v>
       </c>
       <c r="H600" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I600" s="1" t="s">
         <v>12</v>
@@ -16845,7 +16845,7 @@
       <c r="J601" s="2"/>
       <c r="K601" s="1"/>
       <c r="M601" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="602" spans="4:13" x14ac:dyDescent="0.3">
@@ -16859,7 +16859,7 @@
         <v>40</v>
       </c>
       <c r="H602" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I602" s="1" t="s">
         <v>13</v>
@@ -16888,7 +16888,7 @@
         <v>42</v>
       </c>
       <c r="H603" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I603" s="1" t="s">
         <v>10</v>
@@ -16917,7 +16917,7 @@
         <v>95</v>
       </c>
       <c r="H604" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I604" s="1" t="s">
         <v>13</v>
@@ -16946,7 +16946,7 @@
         <v>43</v>
       </c>
       <c r="H605" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I605" s="1" t="s">
         <v>13</v>
@@ -16975,7 +16975,7 @@
         <v>107</v>
       </c>
       <c r="H606" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I606" s="1" t="s">
         <v>13</v>
@@ -17004,7 +17004,7 @@
         <v>44</v>
       </c>
       <c r="H607" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I607" s="1" t="s">
         <v>10</v>
@@ -17033,7 +17033,7 @@
         <v>96</v>
       </c>
       <c r="H608" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I608" s="1" t="s">
         <v>10</v>
@@ -17062,7 +17062,7 @@
         <v>45</v>
       </c>
       <c r="H609" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I609" s="1" t="s">
         <v>10</v>
@@ -17091,7 +17091,7 @@
         <v>47</v>
       </c>
       <c r="H610" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I610" s="1" t="s">
         <v>10</v>
@@ -17120,7 +17120,7 @@
         <v>49</v>
       </c>
       <c r="H611" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I611" s="1" t="s">
         <v>10</v>
@@ -17149,7 +17149,7 @@
         <v>50</v>
       </c>
       <c r="H612" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I612" s="1" t="s">
         <v>10</v>
@@ -17178,7 +17178,7 @@
         <v>52</v>
       </c>
       <c r="H613" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I613" s="1" t="s">
         <v>12</v>
@@ -17201,7 +17201,7 @@
       <c r="J614" s="2"/>
       <c r="K614" s="1"/>
       <c r="M614" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="615" spans="4:13" x14ac:dyDescent="0.3">
@@ -17215,7 +17215,7 @@
         <v>53</v>
       </c>
       <c r="H615" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I615" s="1" t="s">
         <v>10</v>
@@ -17244,7 +17244,7 @@
         <v>55</v>
       </c>
       <c r="H616" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I616" s="1" t="s">
         <v>10</v>
@@ -17273,7 +17273,7 @@
         <v>56</v>
       </c>
       <c r="H617" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I617" s="1" t="s">
         <v>13</v>
@@ -17302,7 +17302,7 @@
         <v>57</v>
       </c>
       <c r="H618" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I618" s="1" t="s">
         <v>13</v>
@@ -17331,7 +17331,7 @@
         <v>58</v>
       </c>
       <c r="H619" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I619" s="1" t="s">
         <v>10</v>
@@ -17360,7 +17360,7 @@
         <v>59</v>
       </c>
       <c r="H620" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I620" s="1" t="s">
         <v>13</v>
@@ -17389,7 +17389,7 @@
         <v>62</v>
       </c>
       <c r="H621" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I621" s="1" t="s">
         <v>10</v>
@@ -17418,7 +17418,7 @@
         <v>63</v>
       </c>
       <c r="H622" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I622" s="1" t="s">
         <v>10</v>
@@ -17447,7 +17447,7 @@
         <v>64</v>
       </c>
       <c r="H623" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I623" s="1" t="s">
         <v>13</v>
@@ -17476,7 +17476,7 @@
         <v>65</v>
       </c>
       <c r="H624" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I624" s="1" t="s">
         <v>10</v>
@@ -17505,7 +17505,7 @@
         <v>66</v>
       </c>
       <c r="H625" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I625" s="1" t="s">
         <v>10</v>
@@ -17534,7 +17534,7 @@
         <v>108</v>
       </c>
       <c r="H626" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I626" s="1" t="s">
         <v>10</v>
@@ -17563,7 +17563,7 @@
         <v>69</v>
       </c>
       <c r="H627" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I627" s="1" t="s">
         <v>10</v>
@@ -17592,7 +17592,7 @@
         <v>70</v>
       </c>
       <c r="H628" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I628" s="1" t="s">
         <v>13</v>
@@ -17621,7 +17621,7 @@
         <v>71</v>
       </c>
       <c r="H629" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I629" s="1" t="s">
         <v>12</v>
@@ -17645,7 +17645,7 @@
       <c r="J630" s="2"/>
       <c r="K630" s="1"/>
       <c r="M630" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="631" spans="4:13" x14ac:dyDescent="0.3">
@@ -17659,7 +17659,7 @@
         <v>99</v>
       </c>
       <c r="H631" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I631" s="1" t="s">
         <v>10</v>
@@ -17688,7 +17688,7 @@
         <v>72</v>
       </c>
       <c r="H632" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I632" s="1" t="s">
         <v>10</v>
@@ -17717,7 +17717,7 @@
         <v>73</v>
       </c>
       <c r="H633" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I633" s="1" t="s">
         <v>13</v>
@@ -17746,7 +17746,7 @@
         <v>100</v>
       </c>
       <c r="H634" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I634" s="1" t="s">
         <v>13</v>
@@ -17775,7 +17775,7 @@
         <v>75</v>
       </c>
       <c r="H635" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I635" s="1" t="s">
         <v>10</v>
@@ -17804,7 +17804,7 @@
         <v>76</v>
       </c>
       <c r="H636" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I636" s="1" t="s">
         <v>13</v>
@@ -17833,7 +17833,7 @@
         <v>101</v>
       </c>
       <c r="H637" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I637" s="1" t="s">
         <v>12</v>
@@ -17857,7 +17857,7 @@
       <c r="J638" s="2"/>
       <c r="K638" s="1"/>
       <c r="M638" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="639" spans="4:13" x14ac:dyDescent="0.3">
@@ -17871,7 +17871,7 @@
         <v>77</v>
       </c>
       <c r="H639" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I639" s="1" t="s">
         <v>10</v>
@@ -17900,7 +17900,7 @@
         <v>78</v>
       </c>
       <c r="H640" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I640" s="1" t="s">
         <v>10</v>
@@ -17929,7 +17929,7 @@
         <v>79</v>
       </c>
       <c r="H641" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I641" s="1" t="s">
         <v>10</v>
@@ -17958,7 +17958,7 @@
         <v>103</v>
       </c>
       <c r="H642" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I642" s="1" t="s">
         <v>10</v>
@@ -17987,7 +17987,7 @@
         <v>81</v>
       </c>
       <c r="H643" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I643" s="1" t="s">
         <v>13</v>
@@ -18016,7 +18016,7 @@
         <v>83</v>
       </c>
       <c r="H644" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I644" s="1" t="s">
         <v>10</v>
@@ -18045,7 +18045,7 @@
         <v>104</v>
       </c>
       <c r="H645" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I645" s="1" t="s">
         <v>13</v>
@@ -18074,7 +18074,7 @@
         <v>85</v>
       </c>
       <c r="H646" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I646" s="1" t="s">
         <v>10</v>
@@ -18103,7 +18103,7 @@
         <v>87</v>
       </c>
       <c r="H647" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I647" s="1" t="s">
         <v>13</v>
@@ -18132,7 +18132,7 @@
         <v>105</v>
       </c>
       <c r="H648" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I648" s="1" t="s">
         <v>13</v>
@@ -18161,7 +18161,7 @@
         <v>88</v>
       </c>
       <c r="H649" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I649" s="1" t="s">
         <v>10</v>
@@ -18417,7 +18417,7 @@
       <c r="J658" s="2"/>
       <c r="K658" s="1"/>
       <c r="M658" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="659" spans="4:13" x14ac:dyDescent="0.3">
@@ -18919,7 +18919,7 @@
       <c r="J676" s="2"/>
       <c r="K676" s="1"/>
       <c r="M676" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="677" spans="4:13" x14ac:dyDescent="0.3">
@@ -19513,7 +19513,7 @@
         <v>106</v>
       </c>
       <c r="H697" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I697" s="1" t="s">
         <v>10</v>
@@ -19542,7 +19542,7 @@
         <v>40</v>
       </c>
       <c r="H698" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I698" s="1" t="s">
         <v>10</v>
@@ -19571,7 +19571,7 @@
         <v>42</v>
       </c>
       <c r="H699" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I699" s="1" t="s">
         <v>10</v>
@@ -19600,7 +19600,7 @@
         <v>95</v>
       </c>
       <c r="H700" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I700" s="1" t="s">
         <v>13</v>
@@ -19629,7 +19629,7 @@
         <v>43</v>
       </c>
       <c r="H701" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I701" s="1" t="s">
         <v>10</v>
@@ -19658,7 +19658,7 @@
         <v>107</v>
       </c>
       <c r="H702" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I702" s="1" t="s">
         <v>10</v>
@@ -19687,7 +19687,7 @@
         <v>44</v>
       </c>
       <c r="H703" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I703" s="1" t="s">
         <v>10</v>
@@ -19716,7 +19716,7 @@
         <v>96</v>
       </c>
       <c r="H704" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I704" s="1" t="s">
         <v>10</v>
@@ -19745,7 +19745,7 @@
         <v>45</v>
       </c>
       <c r="H705" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I705" s="1" t="s">
         <v>10</v>
@@ -19774,7 +19774,7 @@
         <v>47</v>
       </c>
       <c r="H706" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I706" s="1" t="s">
         <v>10</v>
@@ -19803,7 +19803,7 @@
         <v>49</v>
       </c>
       <c r="H707" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I707" s="1" t="s">
         <v>10</v>
@@ -19832,7 +19832,7 @@
         <v>50</v>
       </c>
       <c r="H708" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I708" s="1" t="s">
         <v>10</v>
@@ -19861,7 +19861,7 @@
         <v>52</v>
       </c>
       <c r="H709" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I709" s="1" t="s">
         <v>10</v>
@@ -19890,7 +19890,7 @@
         <v>53</v>
       </c>
       <c r="H710" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I710" s="1" t="s">
         <v>10</v>
@@ -19919,7 +19919,7 @@
         <v>55</v>
       </c>
       <c r="H711" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I711" s="1" t="s">
         <v>10</v>
@@ -19948,7 +19948,7 @@
         <v>56</v>
       </c>
       <c r="H712" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I712" s="1" t="s">
         <v>10</v>
@@ -19977,7 +19977,7 @@
         <v>57</v>
       </c>
       <c r="H713" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I713" s="1" t="s">
         <v>13</v>
@@ -20006,7 +20006,7 @@
         <v>58</v>
       </c>
       <c r="H714" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I714" s="1" t="s">
         <v>10</v>
@@ -20035,7 +20035,7 @@
         <v>59</v>
       </c>
       <c r="H715" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I715" s="1" t="s">
         <v>12</v>
@@ -20059,7 +20059,7 @@
       <c r="J716" s="2"/>
       <c r="K716" s="1"/>
       <c r="M716" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="717" spans="4:13" x14ac:dyDescent="0.3">
@@ -20073,7 +20073,7 @@
         <v>62</v>
       </c>
       <c r="H717" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I717" s="1" t="s">
         <v>10</v>
@@ -20102,7 +20102,7 @@
         <v>63</v>
       </c>
       <c r="H718" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I718" s="1" t="s">
         <v>10</v>
@@ -20131,7 +20131,7 @@
         <v>109</v>
       </c>
       <c r="H719" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I719" s="1" t="s">
         <v>10</v>
@@ -20160,7 +20160,7 @@
         <v>64</v>
       </c>
       <c r="H720" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I720" s="1" t="s">
         <v>13</v>
@@ -20189,7 +20189,7 @@
         <v>65</v>
       </c>
       <c r="H721" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I721" s="1" t="s">
         <v>10</v>
@@ -20218,7 +20218,7 @@
         <v>108</v>
       </c>
       <c r="H722" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I722" s="1" t="s">
         <v>10</v>
@@ -20247,7 +20247,7 @@
         <v>69</v>
       </c>
       <c r="H723" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I723" s="1" t="s">
         <v>10</v>
@@ -20276,7 +20276,7 @@
         <v>70</v>
       </c>
       <c r="H724" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I724" s="1" t="s">
         <v>13</v>
@@ -20305,7 +20305,7 @@
         <v>71</v>
       </c>
       <c r="H725" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I725" s="1" t="s">
         <v>10</v>
@@ -20334,7 +20334,7 @@
         <v>99</v>
       </c>
       <c r="H726" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I726" s="1" t="s">
         <v>10</v>
@@ -20363,7 +20363,7 @@
         <v>72</v>
       </c>
       <c r="H727" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I727" s="1" t="s">
         <v>10</v>
@@ -20392,7 +20392,7 @@
         <v>100</v>
       </c>
       <c r="H728" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I728" s="1" t="s">
         <v>10</v>
@@ -20421,7 +20421,7 @@
         <v>75</v>
       </c>
       <c r="H729" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I729" s="1" t="s">
         <v>10</v>
@@ -20450,7 +20450,7 @@
         <v>76</v>
       </c>
       <c r="H730" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I730" s="1" t="s">
         <v>13</v>
@@ -20479,7 +20479,7 @@
         <v>101</v>
       </c>
       <c r="H731" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I731" s="1" t="s">
         <v>12</v>
@@ -20503,7 +20503,7 @@
       <c r="J732" s="2"/>
       <c r="K732" s="1"/>
       <c r="M732" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="733" spans="4:13" x14ac:dyDescent="0.3">
@@ -20517,7 +20517,7 @@
         <v>77</v>
       </c>
       <c r="H733" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I733" s="1" t="s">
         <v>10</v>
@@ -20546,7 +20546,7 @@
         <v>78</v>
       </c>
       <c r="H734" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I734" s="1" t="s">
         <v>10</v>
@@ -20575,7 +20575,7 @@
         <v>79</v>
       </c>
       <c r="H735" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I735" s="1" t="s">
         <v>10</v>
@@ -20604,7 +20604,7 @@
         <v>103</v>
       </c>
       <c r="H736" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I736" s="1" t="s">
         <v>13</v>
@@ -20633,7 +20633,7 @@
         <v>81</v>
       </c>
       <c r="H737" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I737" s="1" t="s">
         <v>10</v>
@@ -20662,7 +20662,7 @@
         <v>83</v>
       </c>
       <c r="H738" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I738" s="1" t="s">
         <v>10</v>
@@ -20691,7 +20691,7 @@
         <v>104</v>
       </c>
       <c r="H739" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I739" s="1" t="s">
         <v>10</v>
@@ -20720,7 +20720,7 @@
         <v>85</v>
       </c>
       <c r="H740" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I740" s="1" t="s">
         <v>12</v>
@@ -20744,7 +20744,7 @@
       <c r="J741" s="2"/>
       <c r="K741" s="1"/>
       <c r="M741" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="742" spans="4:13" x14ac:dyDescent="0.3">
@@ -20758,7 +20758,7 @@
         <v>87</v>
       </c>
       <c r="H742" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I742" s="1" t="s">
         <v>13</v>
@@ -20787,7 +20787,7 @@
         <v>105</v>
       </c>
       <c r="H743" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I743" s="1" t="s">
         <v>10</v>
@@ -20816,7 +20816,7 @@
         <v>88</v>
       </c>
       <c r="H744" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I744" s="1" t="s">
         <v>10</v>
@@ -20845,7 +20845,7 @@
         <v>96</v>
       </c>
       <c r="H745" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I745" s="1" t="s">
         <v>13</v>
@@ -20874,7 +20874,7 @@
         <v>106</v>
       </c>
       <c r="H746" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I746" s="1" t="s">
         <v>13</v>
@@ -20903,7 +20903,7 @@
         <v>40</v>
       </c>
       <c r="H747" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I747" s="1" t="s">
         <v>13</v>
@@ -20932,7 +20932,7 @@
         <v>42</v>
       </c>
       <c r="H748" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I748" s="1" t="s">
         <v>13</v>
@@ -20961,7 +20961,7 @@
         <v>43</v>
       </c>
       <c r="H749" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I749" s="1" t="s">
         <v>13</v>
@@ -20990,7 +20990,7 @@
         <v>110</v>
       </c>
       <c r="H750" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I750" s="1" t="s">
         <v>13</v>
@@ -21019,7 +21019,7 @@
         <v>107</v>
       </c>
       <c r="H751" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I751" s="1" t="s">
         <v>13</v>
@@ -21048,7 +21048,7 @@
         <v>44</v>
       </c>
       <c r="H752" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I752" s="1" t="s">
         <v>12</v>
@@ -21072,7 +21072,7 @@
       <c r="J753" s="2"/>
       <c r="K753" s="1"/>
       <c r="M753" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="754" spans="4:13" x14ac:dyDescent="0.3">
@@ -21086,7 +21086,7 @@
         <v>96</v>
       </c>
       <c r="H754" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I754" s="1" t="s">
         <v>12</v>
@@ -21110,7 +21110,7 @@
       <c r="J755" s="2"/>
       <c r="K755" s="1"/>
       <c r="M755" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="756" spans="4:13" x14ac:dyDescent="0.3">
@@ -21124,7 +21124,7 @@
         <v>45</v>
       </c>
       <c r="H756" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I756" s="1" t="s">
         <v>10</v>
@@ -21153,7 +21153,7 @@
         <v>47</v>
       </c>
       <c r="H757" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I757" s="1" t="s">
         <v>10</v>
@@ -21182,7 +21182,7 @@
         <v>49</v>
       </c>
       <c r="H758" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I758" s="1" t="s">
         <v>10</v>
@@ -21211,7 +21211,7 @@
         <v>50</v>
       </c>
       <c r="H759" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I759" s="1" t="s">
         <v>10</v>
@@ -21240,7 +21240,7 @@
         <v>52</v>
       </c>
       <c r="H760" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I760" s="1" t="s">
         <v>10</v>
@@ -21269,7 +21269,7 @@
         <v>53</v>
       </c>
       <c r="H761" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I761" s="1" t="s">
         <v>10</v>
@@ -21298,7 +21298,7 @@
         <v>111</v>
       </c>
       <c r="H762" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I762" s="1" t="s">
         <v>12</v>
@@ -21322,7 +21322,7 @@
       <c r="J763" s="2"/>
       <c r="K763" s="1"/>
       <c r="M763" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="764" spans="4:13" x14ac:dyDescent="0.3">
@@ -21336,7 +21336,7 @@
         <v>55</v>
       </c>
       <c r="H764" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I764" s="1" t="s">
         <v>10</v>
@@ -21365,7 +21365,7 @@
         <v>56</v>
       </c>
       <c r="H765" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I765" s="1" t="s">
         <v>13</v>
@@ -21394,7 +21394,7 @@
         <v>57</v>
       </c>
       <c r="H766" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I766" s="1" t="s">
         <v>13</v>
@@ -21423,7 +21423,7 @@
         <v>58</v>
       </c>
       <c r="H767" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I767" s="1" t="s">
         <v>12</v>
@@ -21447,7 +21447,7 @@
       <c r="J768" s="2"/>
       <c r="K768" s="1"/>
       <c r="M768" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="769" spans="4:13" x14ac:dyDescent="0.3">
@@ -21461,7 +21461,7 @@
         <v>59</v>
       </c>
       <c r="H769" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I769" s="1" t="s">
         <v>13</v>
@@ -21490,7 +21490,7 @@
         <v>62</v>
       </c>
       <c r="H770" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I770" s="1" t="s">
         <v>10</v>
@@ -21519,7 +21519,7 @@
         <v>63</v>
       </c>
       <c r="H771" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I771" s="1" t="s">
         <v>10</v>
@@ -21548,7 +21548,7 @@
         <v>109</v>
       </c>
       <c r="H772" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I772" s="1" t="s">
         <v>10</v>
@@ -21577,7 +21577,7 @@
         <v>64</v>
       </c>
       <c r="H773" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I773" s="1" t="s">
         <v>13</v>
@@ -21606,7 +21606,7 @@
         <v>65</v>
       </c>
       <c r="H774" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I774" s="1" t="s">
         <v>10</v>
@@ -21635,7 +21635,7 @@
         <v>108</v>
       </c>
       <c r="H775" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I775" s="1" t="s">
         <v>10</v>
@@ -21664,7 +21664,7 @@
         <v>69</v>
       </c>
       <c r="H776" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I776" s="1" t="s">
         <v>10</v>
@@ -21693,7 +21693,7 @@
         <v>70</v>
       </c>
       <c r="H777" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I777" s="1" t="s">
         <v>10</v>
@@ -21722,7 +21722,7 @@
         <v>71</v>
       </c>
       <c r="H778" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I778" s="1" t="s">
         <v>10</v>
@@ -21751,7 +21751,7 @@
         <v>99</v>
       </c>
       <c r="H779" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I779" s="1" t="s">
         <v>10</v>
@@ -21780,7 +21780,7 @@
         <v>72</v>
       </c>
       <c r="H780" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I780" s="1" t="s">
         <v>10</v>
@@ -21809,7 +21809,7 @@
         <v>100</v>
       </c>
       <c r="H781" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I781" s="1" t="s">
         <v>12</v>
@@ -21831,7 +21831,7 @@
       <c r="I782" s="1"/>
       <c r="K782" s="1"/>
       <c r="M782" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="783" spans="4:13" x14ac:dyDescent="0.3">
@@ -21845,7 +21845,7 @@
         <v>75</v>
       </c>
       <c r="H783" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I783" s="1" t="s">
         <v>10</v>
@@ -21874,7 +21874,7 @@
         <v>76</v>
       </c>
       <c r="H784" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I784" s="1" t="s">
         <v>13</v>
@@ -21903,7 +21903,7 @@
         <v>101</v>
       </c>
       <c r="H785" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I785" s="1" t="s">
         <v>13</v>
@@ -21932,7 +21932,7 @@
         <v>77</v>
       </c>
       <c r="H786" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I786" s="1" t="s">
         <v>10</v>
@@ -21961,7 +21961,7 @@
         <v>78</v>
       </c>
       <c r="H787" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I787" s="1" t="s">
         <v>10</v>
@@ -21990,7 +21990,7 @@
         <v>79</v>
       </c>
       <c r="H788" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I788" s="1" t="s">
         <v>13</v>
@@ -22019,7 +22019,7 @@
         <v>81</v>
       </c>
       <c r="H789" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I789" s="1" t="s">
         <v>12</v>
@@ -22043,7 +22043,7 @@
       <c r="J790" s="2"/>
       <c r="K790" s="1"/>
       <c r="M790" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="791" spans="4:13" x14ac:dyDescent="0.3">
@@ -22057,7 +22057,7 @@
         <v>83</v>
       </c>
       <c r="H791" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I791" s="1" t="s">
         <v>10</v>
@@ -22086,7 +22086,7 @@
         <v>104</v>
       </c>
       <c r="H792" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I792" s="1" t="s">
         <v>10</v>
@@ -22115,7 +22115,7 @@
         <v>85</v>
       </c>
       <c r="H793" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I793" s="1" t="s">
         <v>10</v>
@@ -22144,12 +22144,12 @@
         <v>87</v>
       </c>
       <c r="H794" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I794" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J794">
+      <c r="J794" s="2">
         <v>0</v>
       </c>
       <c r="K794" s="1">
@@ -22173,7 +22173,7 @@
         <v>105</v>
       </c>
       <c r="H795" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I795" s="1" t="s">
         <v>10</v>
@@ -22202,7 +22202,7 @@
         <v>88</v>
       </c>
       <c r="H796" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I796" s="1" t="s">
         <v>10</v>
@@ -22231,7 +22231,7 @@
         <v>106</v>
       </c>
       <c r="H797" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I797" s="1" t="s">
         <v>13</v>
@@ -22260,7 +22260,7 @@
         <v>40</v>
       </c>
       <c r="H798" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I798" s="1" t="s">
         <v>13</v>
@@ -22289,7 +22289,7 @@
         <v>42</v>
       </c>
       <c r="H799" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I799" s="1" t="s">
         <v>13</v>
@@ -22318,7 +22318,7 @@
         <v>43</v>
       </c>
       <c r="H800" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I800" s="1" t="s">
         <v>10</v>
@@ -22347,7 +22347,7 @@
         <v>110</v>
       </c>
       <c r="H801" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I801" s="1" t="s">
         <v>13</v>
@@ -22376,7 +22376,7 @@
         <v>107</v>
       </c>
       <c r="H802" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I802" s="1" t="s">
         <v>13</v>
@@ -22405,7 +22405,7 @@
         <v>44</v>
       </c>
       <c r="H803" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I803" s="1" t="s">
         <v>10</v>
@@ -22434,7 +22434,7 @@
         <v>96</v>
       </c>
       <c r="H804" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I804" s="1" t="s">
         <v>10</v>
@@ -22463,7 +22463,7 @@
         <v>45</v>
       </c>
       <c r="H805" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I805" s="1" t="s">
         <v>10</v>
@@ -22492,7 +22492,7 @@
         <v>47</v>
       </c>
       <c r="H806" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I806" s="1" t="s">
         <v>13</v>
@@ -22521,7 +22521,7 @@
         <v>49</v>
       </c>
       <c r="H807" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I807" s="1" t="s">
         <v>10</v>
@@ -22550,7 +22550,7 @@
         <v>50</v>
       </c>
       <c r="H808" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I808" s="1" t="s">
         <v>10</v>
@@ -22579,7 +22579,7 @@
         <v>52</v>
       </c>
       <c r="H809" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I809" s="1" t="s">
         <v>10</v>
@@ -22608,7 +22608,7 @@
         <v>53</v>
       </c>
       <c r="H810" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I810" s="1" t="s">
         <v>10</v>
@@ -22637,7 +22637,7 @@
         <v>111</v>
       </c>
       <c r="H811" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I811" s="1" t="s">
         <v>10</v>
@@ -22666,7 +22666,7 @@
         <v>55</v>
       </c>
       <c r="H812" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I812" s="1" t="s">
         <v>10</v>
@@ -22695,7 +22695,7 @@
         <v>57</v>
       </c>
       <c r="H813" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I813" s="1" t="s">
         <v>13</v>
@@ -22724,7 +22724,7 @@
         <v>58</v>
       </c>
       <c r="H814" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I814" s="1" t="s">
         <v>13</v>
@@ -22753,7 +22753,7 @@
         <v>59</v>
       </c>
       <c r="H815" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I815" s="1" t="s">
         <v>10</v>
@@ -22782,7 +22782,7 @@
         <v>62</v>
       </c>
       <c r="H816" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I816" s="1" t="s">
         <v>10</v>
@@ -22811,7 +22811,7 @@
         <v>63</v>
       </c>
       <c r="H817" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I817" s="1" t="s">
         <v>10</v>
@@ -22840,7 +22840,7 @@
         <v>109</v>
       </c>
       <c r="H818" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I818" s="1" t="s">
         <v>10</v>
@@ -22869,7 +22869,7 @@
         <v>64</v>
       </c>
       <c r="H819" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I819" s="1" t="s">
         <v>13</v>
@@ -22898,7 +22898,7 @@
         <v>65</v>
       </c>
       <c r="H820" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I820" s="1" t="s">
         <v>10</v>
@@ -22927,7 +22927,7 @@
         <v>108</v>
       </c>
       <c r="H821" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I821" s="1" t="s">
         <v>13</v>
@@ -22956,7 +22956,7 @@
         <v>69</v>
       </c>
       <c r="H822" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I822" s="1" t="s">
         <v>10</v>
@@ -22985,7 +22985,7 @@
         <v>70</v>
       </c>
       <c r="H823" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I823" s="1" t="s">
         <v>14</v>
@@ -23009,7 +23009,7 @@
       <c r="J824" s="2"/>
       <c r="K824" s="1"/>
       <c r="M824" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="825" spans="4:13" x14ac:dyDescent="0.3">
@@ -23023,7 +23023,7 @@
         <v>71</v>
       </c>
       <c r="H825" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I825" s="1" t="s">
         <v>10</v>
@@ -23052,7 +23052,7 @@
         <v>99</v>
       </c>
       <c r="H826" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I826" s="1" t="s">
         <v>10</v>
@@ -23081,7 +23081,7 @@
         <v>72</v>
       </c>
       <c r="H827" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I827" s="1" t="s">
         <v>13</v>
@@ -23110,7 +23110,7 @@
         <v>100</v>
       </c>
       <c r="H828" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I828" s="1" t="s">
         <v>10</v>
@@ -23139,7 +23139,7 @@
         <v>75</v>
       </c>
       <c r="H829" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I829" s="1" t="s">
         <v>10</v>
@@ -23168,7 +23168,7 @@
         <v>76</v>
       </c>
       <c r="H830" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I830" s="1" t="s">
         <v>13</v>
@@ -23197,7 +23197,7 @@
         <v>101</v>
       </c>
       <c r="H831" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I831" s="1" t="s">
         <v>13</v>
@@ -23226,7 +23226,7 @@
         <v>77</v>
       </c>
       <c r="H832" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I832" s="1" t="s">
         <v>10</v>
@@ -23255,7 +23255,7 @@
         <v>78</v>
       </c>
       <c r="H833" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I833" s="1" t="s">
         <v>10</v>
@@ -23284,7 +23284,7 @@
         <v>79</v>
       </c>
       <c r="H834" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I834" s="1" t="s">
         <v>13</v>
@@ -23313,7 +23313,7 @@
         <v>112</v>
       </c>
       <c r="H835" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I835" s="1" t="s">
         <v>10</v>
@@ -23342,7 +23342,7 @@
         <v>81</v>
       </c>
       <c r="H836" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I836" s="1" t="s">
         <v>13</v>
@@ -23371,7 +23371,7 @@
         <v>83</v>
       </c>
       <c r="H837" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I837" s="1" t="s">
         <v>13</v>
@@ -23400,7 +23400,7 @@
         <v>104</v>
       </c>
       <c r="H838" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I838" s="1" t="s">
         <v>10</v>
@@ -23429,7 +23429,7 @@
         <v>85</v>
       </c>
       <c r="H839" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I839" s="1" t="s">
         <v>10</v>
@@ -23458,7 +23458,7 @@
         <v>87</v>
       </c>
       <c r="H840" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I840" s="1" t="s">
         <v>13</v>
@@ -23487,7 +23487,7 @@
         <v>105</v>
       </c>
       <c r="H841" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I841" s="1" t="s">
         <v>10</v>
@@ -23516,7 +23516,7 @@
         <v>88</v>
       </c>
       <c r="H842" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I842" s="1" t="s">
         <v>10</v>
@@ -23545,7 +23545,7 @@
         <v>106</v>
       </c>
       <c r="H843" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I843" s="1" t="s">
         <v>13</v>
@@ -23574,7 +23574,7 @@
         <v>40</v>
       </c>
       <c r="H844" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I844" s="1" t="s">
         <v>13</v>
@@ -23603,7 +23603,7 @@
         <v>42</v>
       </c>
       <c r="H845" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I845" s="1" t="s">
         <v>13</v>
@@ -23632,7 +23632,7 @@
         <v>43</v>
       </c>
       <c r="H846" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I846" s="1" t="s">
         <v>13</v>
@@ -23661,7 +23661,7 @@
         <v>110</v>
       </c>
       <c r="H847" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I847" s="1" t="s">
         <v>13</v>
@@ -23690,7 +23690,7 @@
         <v>107</v>
       </c>
       <c r="H848" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I848" s="1" t="s">
         <v>13</v>
@@ -23719,7 +23719,7 @@
         <v>44</v>
       </c>
       <c r="H849" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I849" s="1" t="s">
         <v>10</v>
@@ -23748,7 +23748,7 @@
         <v>96</v>
       </c>
       <c r="H850" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I850" s="1" t="s">
         <v>13</v>
@@ -23777,7 +23777,7 @@
         <v>45</v>
       </c>
       <c r="H851" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I851" s="1" t="s">
         <v>10</v>
@@ -23806,7 +23806,7 @@
         <v>47</v>
       </c>
       <c r="H852" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I852" s="1" t="s">
         <v>10</v>
@@ -23835,7 +23835,7 @@
         <v>49</v>
       </c>
       <c r="H853" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I853" s="1" t="s">
         <v>10</v>
@@ -23864,7 +23864,7 @@
         <v>50</v>
       </c>
       <c r="H854" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I854" s="1" t="s">
         <v>10</v>
@@ -23893,7 +23893,7 @@
         <v>52</v>
       </c>
       <c r="H855" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I855" s="1" t="s">
         <v>10</v>
@@ -23922,7 +23922,7 @@
         <v>53</v>
       </c>
       <c r="H856" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I856" s="1" t="s">
         <v>10</v>
@@ -23951,7 +23951,7 @@
         <v>111</v>
       </c>
       <c r="H857" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I857" s="1" t="s">
         <v>13</v>
@@ -23980,7 +23980,7 @@
         <v>55</v>
       </c>
       <c r="H858" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I858" s="1" t="s">
         <v>10</v>
@@ -24009,7 +24009,7 @@
         <v>57</v>
       </c>
       <c r="H859" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I859" s="1" t="s">
         <v>13</v>
@@ -24038,7 +24038,7 @@
         <v>58</v>
       </c>
       <c r="H860" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I860" s="1" t="s">
         <v>12</v>
@@ -24062,7 +24062,7 @@
       <c r="J861" s="2"/>
       <c r="K861" s="1"/>
       <c r="M861" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="862" spans="4:13" x14ac:dyDescent="0.3">
@@ -24076,7 +24076,7 @@
         <v>59</v>
       </c>
       <c r="H862" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I862" s="1" t="s">
         <v>13</v>
@@ -24105,7 +24105,7 @@
         <v>62</v>
       </c>
       <c r="H863" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I863" s="1" t="s">
         <v>10</v>
@@ -24134,7 +24134,7 @@
         <v>63</v>
       </c>
       <c r="H864" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I864" s="1" t="s">
         <v>10</v>
@@ -24163,7 +24163,7 @@
         <v>109</v>
       </c>
       <c r="H865" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I865" s="1" t="s">
         <v>10</v>
@@ -24192,7 +24192,7 @@
         <v>64</v>
       </c>
       <c r="H866" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I866" s="1" t="s">
         <v>13</v>
@@ -24221,7 +24221,7 @@
         <v>65</v>
       </c>
       <c r="H867" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I867" s="1" t="s">
         <v>10</v>
@@ -24250,7 +24250,7 @@
         <v>108</v>
       </c>
       <c r="H868" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I868" s="1" t="s">
         <v>13</v>
@@ -24279,7 +24279,7 @@
         <v>69</v>
       </c>
       <c r="H869" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I869" s="1" t="s">
         <v>10</v>
@@ -24308,7 +24308,7 @@
         <v>70</v>
       </c>
       <c r="H870" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I870" s="1" t="s">
         <v>13</v>
@@ -24337,7 +24337,7 @@
         <v>71</v>
       </c>
       <c r="H871" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I871" s="1" t="s">
         <v>12</v>
@@ -24360,7 +24360,7 @@
       <c r="J872" s="2"/>
       <c r="K872" s="1"/>
       <c r="M872" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="873" spans="4:13" x14ac:dyDescent="0.3">
@@ -24374,7 +24374,7 @@
         <v>99</v>
       </c>
       <c r="H873" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I873" s="1" t="s">
         <v>10</v>
@@ -24403,7 +24403,7 @@
         <v>72</v>
       </c>
       <c r="H874" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I874" s="1" t="s">
         <v>10</v>
@@ -24432,7 +24432,7 @@
         <v>100</v>
       </c>
       <c r="H875" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I875" s="1" t="s">
         <v>10</v>
@@ -24461,7 +24461,7 @@
         <v>75</v>
       </c>
       <c r="H876" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I876" s="1" t="s">
         <v>14</v>
@@ -24485,7 +24485,7 @@
       <c r="J877" s="2"/>
       <c r="K877" s="1"/>
       <c r="M877" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="878" spans="4:13" x14ac:dyDescent="0.3">
@@ -24499,7 +24499,7 @@
         <v>76</v>
       </c>
       <c r="H878" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I878" s="1" t="s">
         <v>13</v>
@@ -24528,7 +24528,7 @@
         <v>101</v>
       </c>
       <c r="H879" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I879" s="1" t="s">
         <v>13</v>
@@ -24557,7 +24557,7 @@
         <v>77</v>
       </c>
       <c r="H880" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I880" s="1" t="s">
         <v>10</v>
@@ -24586,7 +24586,7 @@
         <v>78</v>
       </c>
       <c r="H881" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I881" s="1" t="s">
         <v>10</v>
@@ -24615,7 +24615,7 @@
         <v>79</v>
       </c>
       <c r="H882" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I882" s="1" t="s">
         <v>13</v>
@@ -24644,7 +24644,7 @@
         <v>112</v>
       </c>
       <c r="H883" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I883" s="1" t="s">
         <v>10</v>
@@ -24673,7 +24673,7 @@
         <v>81</v>
       </c>
       <c r="H884" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I884" s="1" t="s">
         <v>13</v>
@@ -24702,7 +24702,7 @@
         <v>83</v>
       </c>
       <c r="H885" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I885" s="1" t="s">
         <v>13</v>
@@ -24731,7 +24731,7 @@
         <v>104</v>
       </c>
       <c r="H886" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I886" s="1" t="s">
         <v>10</v>
@@ -24760,7 +24760,7 @@
         <v>85</v>
       </c>
       <c r="H887" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I887" s="1" t="s">
         <v>10</v>
@@ -24789,7 +24789,7 @@
         <v>87</v>
       </c>
       <c r="H888" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I888" s="1" t="s">
         <v>13</v>
@@ -24818,7 +24818,7 @@
         <v>105</v>
       </c>
       <c r="H889" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I889" s="1" t="s">
         <v>10</v>
@@ -24847,7 +24847,7 @@
         <v>113</v>
       </c>
       <c r="H890" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I890" s="1" t="s">
         <v>10</v>
@@ -24876,7 +24876,7 @@
         <v>88</v>
       </c>
       <c r="H891" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I891" s="1" t="s">
         <v>10</v>
@@ -24905,7 +24905,7 @@
         <v>106</v>
       </c>
       <c r="H892" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I892" s="1" t="s">
         <v>13</v>
@@ -24934,7 +24934,7 @@
         <v>42</v>
       </c>
       <c r="H893" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I893" s="1" t="s">
         <v>13</v>
@@ -24963,7 +24963,7 @@
         <v>43</v>
       </c>
       <c r="H894" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I894" s="1" t="s">
         <v>10</v>
@@ -24992,7 +24992,7 @@
         <v>107</v>
       </c>
       <c r="H895" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I895" s="1" t="s">
         <v>13</v>
@@ -25021,7 +25021,7 @@
         <v>44</v>
       </c>
       <c r="H896" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I896" s="1" t="s">
         <v>10</v>
@@ -25050,7 +25050,7 @@
         <v>96</v>
       </c>
       <c r="H897" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I897" s="1" t="s">
         <v>10</v>
@@ -25079,7 +25079,7 @@
         <v>45</v>
       </c>
       <c r="H898" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I898" s="1" t="s">
         <v>10</v>
@@ -25108,7 +25108,7 @@
         <v>47</v>
       </c>
       <c r="H899" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I899" s="1" t="s">
         <v>10</v>
@@ -25137,7 +25137,7 @@
         <v>49</v>
       </c>
       <c r="H900" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I900" s="1" t="s">
         <v>10</v>
@@ -25166,7 +25166,7 @@
         <v>50</v>
       </c>
       <c r="H901" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I901" s="1" t="s">
         <v>10</v>
@@ -25195,7 +25195,7 @@
         <v>114</v>
       </c>
       <c r="H902" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I902" s="1" t="s">
         <v>10</v>
@@ -25224,7 +25224,7 @@
         <v>52</v>
       </c>
       <c r="H903" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I903" s="1" t="s">
         <v>10</v>
@@ -25253,7 +25253,7 @@
         <v>53</v>
       </c>
       <c r="H904" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I904" s="1" t="s">
         <v>10</v>
@@ -25282,7 +25282,7 @@
         <v>111</v>
       </c>
       <c r="H905" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I905" s="1" t="s">
         <v>10</v>
@@ -25311,7 +25311,7 @@
         <v>55</v>
       </c>
       <c r="H906" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I906" s="1" t="s">
         <v>10</v>
@@ -25340,7 +25340,7 @@
         <v>57</v>
       </c>
       <c r="H907" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I907" s="1" t="s">
         <v>13</v>
@@ -25369,7 +25369,7 @@
         <v>58</v>
       </c>
       <c r="H908" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I908" s="1" t="s">
         <v>10</v>
@@ -25398,7 +25398,7 @@
         <v>59</v>
       </c>
       <c r="H909" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I909" s="1" t="s">
         <v>10</v>
@@ -25427,7 +25427,7 @@
         <v>62</v>
       </c>
       <c r="H910" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I910" s="1" t="s">
         <v>10</v>
@@ -25456,7 +25456,7 @@
         <v>63</v>
       </c>
       <c r="H911" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I911" s="1" t="s">
         <v>10</v>
@@ -25485,7 +25485,7 @@
         <v>109</v>
       </c>
       <c r="H912" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I912" s="1" t="s">
         <v>13</v>
@@ -25514,7 +25514,7 @@
         <v>64</v>
       </c>
       <c r="H913" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I913" s="1" t="s">
         <v>13</v>
@@ -25543,7 +25543,7 @@
         <v>65</v>
       </c>
       <c r="H914" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I914" s="1" t="s">
         <v>10</v>
@@ -25572,7 +25572,7 @@
         <v>69</v>
       </c>
       <c r="H915" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I915" s="1" t="s">
         <v>10</v>
@@ -25601,7 +25601,7 @@
         <v>70</v>
       </c>
       <c r="H916" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I916" s="1" t="s">
         <v>14</v>
@@ -25625,7 +25625,7 @@
       <c r="J917" s="2"/>
       <c r="K917" s="1"/>
       <c r="M917" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="918" spans="4:13" x14ac:dyDescent="0.3">
@@ -25639,7 +25639,7 @@
         <v>71</v>
       </c>
       <c r="H918" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I918" s="1" t="s">
         <v>10</v>
@@ -25668,7 +25668,7 @@
         <v>99</v>
       </c>
       <c r="H919" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I919" s="1" t="s">
         <v>10</v>
@@ -25697,7 +25697,7 @@
         <v>72</v>
       </c>
       <c r="H920" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I920" s="1" t="s">
         <v>13</v>
@@ -25726,7 +25726,7 @@
         <v>100</v>
       </c>
       <c r="H921" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I921" s="1" t="s">
         <v>10</v>
@@ -25755,7 +25755,7 @@
         <v>75</v>
       </c>
       <c r="H922" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I922" s="1" t="s">
         <v>10</v>
@@ -25784,7 +25784,7 @@
         <v>76</v>
       </c>
       <c r="H923" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I923" s="1" t="s">
         <v>13</v>
@@ -25813,7 +25813,7 @@
         <v>101</v>
       </c>
       <c r="H924" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I924" s="1" t="s">
         <v>13</v>
@@ -25842,7 +25842,7 @@
         <v>77</v>
       </c>
       <c r="H925" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I925" s="1" t="s">
         <v>13</v>
@@ -25871,7 +25871,7 @@
         <v>78</v>
       </c>
       <c r="H926" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I926" s="1" t="s">
         <v>10</v>
@@ -25900,7 +25900,7 @@
         <v>79</v>
       </c>
       <c r="H927" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I927" s="1" t="s">
         <v>10</v>
@@ -25929,7 +25929,7 @@
         <v>112</v>
       </c>
       <c r="H928" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I928" s="1" t="s">
         <v>10</v>
@@ -25958,7 +25958,7 @@
         <v>81</v>
       </c>
       <c r="H929" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I929" s="1" t="s">
         <v>12</v>
@@ -25982,7 +25982,7 @@
       <c r="J930" s="2"/>
       <c r="K930" s="1"/>
       <c r="M930" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="931" spans="4:13" x14ac:dyDescent="0.3">
@@ -25996,7 +25996,7 @@
         <v>83</v>
       </c>
       <c r="H931" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I931" s="1" t="s">
         <v>10</v>
@@ -26025,7 +26025,7 @@
         <v>104</v>
       </c>
       <c r="H932" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I932" s="1" t="s">
         <v>10</v>
@@ -26054,7 +26054,7 @@
         <v>87</v>
       </c>
       <c r="H933" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I933" s="1" t="s">
         <v>13</v>
@@ -26083,7 +26083,7 @@
         <v>105</v>
       </c>
       <c r="H934" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I934" s="1" t="s">
         <v>10</v>
@@ -26112,7 +26112,7 @@
         <v>113</v>
       </c>
       <c r="H935" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I935" s="1" t="s">
         <v>10</v>
@@ -26141,7 +26141,7 @@
         <v>88</v>
       </c>
       <c r="H936" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I936" s="1" t="s">
         <v>13</v>
@@ -26170,7 +26170,7 @@
         <v>106</v>
       </c>
       <c r="H937" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I937" s="1" t="s">
         <v>13</v>
@@ -26199,7 +26199,7 @@
         <v>42</v>
       </c>
       <c r="H938" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I938" s="1" t="s">
         <v>13</v>
@@ -26228,7 +26228,7 @@
         <v>43</v>
       </c>
       <c r="H939" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I939" s="1" t="s">
         <v>10</v>
@@ -26257,7 +26257,7 @@
         <v>107</v>
       </c>
       <c r="H940" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I940" s="1" t="s">
         <v>13</v>
@@ -26286,7 +26286,7 @@
         <v>44</v>
       </c>
       <c r="H941" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I941" s="1" t="s">
         <v>10</v>
@@ -26315,7 +26315,7 @@
         <v>96</v>
       </c>
       <c r="H942" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I942" s="1" t="s">
         <v>10</v>
@@ -26344,7 +26344,7 @@
         <v>45</v>
       </c>
       <c r="H943" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I943" s="1" t="s">
         <v>10</v>
@@ -26373,7 +26373,7 @@
         <v>47</v>
       </c>
       <c r="H944" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I944" s="1" t="s">
         <v>12</v>
@@ -26397,7 +26397,7 @@
       <c r="J945" s="2"/>
       <c r="K945" s="1"/>
       <c r="M945" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="946" spans="4:13" x14ac:dyDescent="0.3">
@@ -26411,7 +26411,7 @@
         <v>49</v>
       </c>
       <c r="H946" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I946" s="1" t="s">
         <v>10</v>
@@ -26440,7 +26440,7 @@
         <v>50</v>
       </c>
       <c r="H947" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I947" s="1" t="s">
         <v>10</v>
@@ -26469,7 +26469,7 @@
         <v>52</v>
       </c>
       <c r="H948" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I948" s="1" t="s">
         <v>10</v>
@@ -26498,7 +26498,7 @@
         <v>53</v>
       </c>
       <c r="H949" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I949" s="1" t="s">
         <v>10</v>
@@ -26527,7 +26527,7 @@
         <v>111</v>
       </c>
       <c r="H950" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I950" s="1" t="s">
         <v>10</v>
@@ -26556,7 +26556,7 @@
         <v>55</v>
       </c>
       <c r="H951" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I951" s="1" t="s">
         <v>12</v>
@@ -26580,7 +26580,7 @@
       <c r="J952" s="2"/>
       <c r="K952" s="1"/>
       <c r="M952" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="953" spans="4:13" x14ac:dyDescent="0.3">
@@ -26594,7 +26594,7 @@
         <v>57</v>
       </c>
       <c r="H953" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I953" s="1" t="s">
         <v>13</v>
@@ -26623,7 +26623,7 @@
         <v>58</v>
       </c>
       <c r="H954" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I954" s="1" t="s">
         <v>10</v>
@@ -26652,7 +26652,7 @@
         <v>59</v>
       </c>
       <c r="H955" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I955" s="1" t="s">
         <v>12</v>
@@ -26676,7 +26676,7 @@
       <c r="J956" s="2"/>
       <c r="K956" s="1"/>
       <c r="M956" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="957" spans="4:13" x14ac:dyDescent="0.3">
@@ -26690,7 +26690,7 @@
         <v>62</v>
       </c>
       <c r="H957" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I957" s="1" t="s">
         <v>10</v>
@@ -26719,7 +26719,7 @@
         <v>63</v>
       </c>
       <c r="H958" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I958" s="1" t="s">
         <v>10</v>
@@ -26748,7 +26748,7 @@
         <v>109</v>
       </c>
       <c r="H959" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I959" s="1" t="s">
         <v>10</v>
@@ -26777,7 +26777,7 @@
         <v>64</v>
       </c>
       <c r="H960" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I960" s="1" t="s">
         <v>13</v>
@@ -26806,7 +26806,7 @@
         <v>65</v>
       </c>
       <c r="H961" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I961" s="1" t="s">
         <v>10</v>
@@ -26835,7 +26835,7 @@
         <v>69</v>
       </c>
       <c r="H962" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I962" s="1" t="s">
         <v>10</v>
@@ -26864,7 +26864,7 @@
         <v>70</v>
       </c>
       <c r="H963" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I963" s="1" t="s">
         <v>10</v>
@@ -26893,7 +26893,7 @@
         <v>71</v>
       </c>
       <c r="H964" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I964" s="1" t="s">
         <v>10</v>
@@ -26922,7 +26922,7 @@
         <v>99</v>
       </c>
       <c r="H965" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I965" s="1" t="s">
         <v>10</v>
@@ -26951,7 +26951,7 @@
         <v>72</v>
       </c>
       <c r="H966" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I966" s="1" t="s">
         <v>10</v>
@@ -26980,7 +26980,7 @@
         <v>100</v>
       </c>
       <c r="H967" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I967" s="1" t="s">
         <v>10</v>
@@ -27009,7 +27009,7 @@
         <v>75</v>
       </c>
       <c r="H968" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I968" s="1" t="s">
         <v>12</v>
@@ -27033,7 +27033,7 @@
       <c r="J969" s="2"/>
       <c r="K969" s="1"/>
       <c r="M969" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="970" spans="4:13" x14ac:dyDescent="0.3">
@@ -27047,7 +27047,7 @@
         <v>101</v>
       </c>
       <c r="H970" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I970" s="1" t="s">
         <v>13</v>
@@ -27076,7 +27076,7 @@
         <v>77</v>
       </c>
       <c r="H971" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I971" s="1" t="s">
         <v>13</v>
@@ -27105,7 +27105,7 @@
         <v>78</v>
       </c>
       <c r="H972" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I972" s="1" t="s">
         <v>12</v>
@@ -27129,7 +27129,7 @@
       <c r="J973" s="2"/>
       <c r="K973" s="1"/>
       <c r="M973" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="974" spans="4:13" x14ac:dyDescent="0.3">
@@ -27143,7 +27143,7 @@
         <v>79</v>
       </c>
       <c r="H974" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I974" s="1" t="s">
         <v>13</v>
@@ -27172,7 +27172,7 @@
         <v>112</v>
       </c>
       <c r="H975" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I975" s="1" t="s">
         <v>10</v>
@@ -27201,7 +27201,7 @@
         <v>81</v>
       </c>
       <c r="H976" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I976" s="1" t="s">
         <v>12</v>
@@ -27224,7 +27224,7 @@
       <c r="I977" s="1"/>
       <c r="K977" s="1"/>
       <c r="M977" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="978" spans="4:13" x14ac:dyDescent="0.3">
@@ -27238,7 +27238,7 @@
         <v>83</v>
       </c>
       <c r="H978" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I978" s="1" t="s">
         <v>10</v>
@@ -27267,7 +27267,7 @@
         <v>104</v>
       </c>
       <c r="H979" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I979" s="1" t="s">
         <v>10</v>
@@ -27296,7 +27296,7 @@
         <v>105</v>
       </c>
       <c r="H980" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I980" s="1" t="s">
         <v>10</v>
@@ -27325,7 +27325,7 @@
         <v>113</v>
       </c>
       <c r="H981" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I981" s="1" t="s">
         <v>10</v>
@@ -27784,7 +27784,7 @@
       <c r="J997" s="2"/>
       <c r="K997" s="1"/>
       <c r="M997" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="998" spans="4:13" x14ac:dyDescent="0.3">
@@ -28112,7 +28112,7 @@
       <c r="J1009" s="2"/>
       <c r="K1009" s="1"/>
       <c r="M1009" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1010" spans="4:13" x14ac:dyDescent="0.3">
@@ -28614,7 +28614,7 @@
       <c r="J1027" s="2"/>
       <c r="K1027" s="1"/>
       <c r="M1027" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1028" spans="4:13" x14ac:dyDescent="0.3">
@@ -28679,7 +28679,7 @@
       <c r="I1030" s="1"/>
       <c r="K1030" s="1"/>
       <c r="M1030" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1031" spans="4:13" x14ac:dyDescent="0.3">
@@ -29708,7 +29708,7 @@
         <v>106</v>
       </c>
       <c r="H1066" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1066" s="1" t="s">
         <v>13</v>
@@ -29737,7 +29737,7 @@
         <v>42</v>
       </c>
       <c r="H1067" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1067" s="1" t="s">
         <v>13</v>
@@ -29766,7 +29766,7 @@
         <v>43</v>
       </c>
       <c r="H1068" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1068" s="1" t="s">
         <v>10</v>
@@ -29795,7 +29795,7 @@
         <v>107</v>
       </c>
       <c r="H1069" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1069" s="1" t="s">
         <v>13</v>
@@ -29824,7 +29824,7 @@
         <v>44</v>
       </c>
       <c r="H1070" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1070" s="1" t="s">
         <v>12</v>
@@ -29847,7 +29847,7 @@
       <c r="I1071" s="1"/>
       <c r="K1071" s="1"/>
       <c r="M1071" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1072" spans="4:13" x14ac:dyDescent="0.3">
@@ -29861,7 +29861,7 @@
         <v>117</v>
       </c>
       <c r="H1072" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1072" s="1" t="s">
         <v>13</v>
@@ -29890,7 +29890,7 @@
         <v>96</v>
       </c>
       <c r="H1073" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1073" s="1" t="s">
         <v>10</v>
@@ -29919,7 +29919,7 @@
         <v>119</v>
       </c>
       <c r="H1074" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1074" s="1" t="s">
         <v>10</v>
@@ -29948,7 +29948,7 @@
         <v>45</v>
       </c>
       <c r="H1075" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1075" s="1" t="s">
         <v>10</v>
@@ -29977,7 +29977,7 @@
         <v>115</v>
       </c>
       <c r="H1076" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1076" s="1" t="s">
         <v>10</v>
@@ -30006,7 +30006,7 @@
         <v>47</v>
       </c>
       <c r="H1077" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1077" s="1" t="s">
         <v>13</v>
@@ -30035,7 +30035,7 @@
         <v>49</v>
       </c>
       <c r="H1078" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1078" s="1" t="s">
         <v>10</v>
@@ -30064,7 +30064,7 @@
         <v>50</v>
       </c>
       <c r="H1079" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1079" s="1" t="s">
         <v>10</v>
@@ -30093,7 +30093,7 @@
         <v>52</v>
       </c>
       <c r="H1080" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1080" s="1" t="s">
         <v>10</v>
@@ -30122,7 +30122,7 @@
         <v>53</v>
       </c>
       <c r="H1081" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1081" s="1" t="s">
         <v>13</v>
@@ -30151,7 +30151,7 @@
         <v>55</v>
       </c>
       <c r="H1082" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1082" s="1" t="s">
         <v>10</v>
@@ -30180,7 +30180,7 @@
         <v>57</v>
       </c>
       <c r="H1083" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1083" s="1" t="s">
         <v>13</v>
@@ -30209,7 +30209,7 @@
         <v>58</v>
       </c>
       <c r="H1084" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1084" s="1" t="s">
         <v>10</v>
@@ -30238,7 +30238,7 @@
         <v>59</v>
       </c>
       <c r="H1085" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1085" s="1" t="s">
         <v>12</v>
@@ -30262,7 +30262,7 @@
       <c r="J1086" s="2"/>
       <c r="K1086" s="1"/>
       <c r="M1086" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1087" spans="4:13" x14ac:dyDescent="0.3">
@@ -30276,7 +30276,7 @@
         <v>62</v>
       </c>
       <c r="H1087" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1087" s="1" t="s">
         <v>10</v>
@@ -30305,7 +30305,7 @@
         <v>118</v>
       </c>
       <c r="H1088" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1088" s="1" t="s">
         <v>13</v>
@@ -30334,7 +30334,7 @@
         <v>63</v>
       </c>
       <c r="H1089" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1089" s="1" t="s">
         <v>10</v>
@@ -30363,7 +30363,7 @@
         <v>109</v>
       </c>
       <c r="H1090" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1090" s="1" t="s">
         <v>12</v>
@@ -30387,7 +30387,7 @@
       <c r="J1091" s="2"/>
       <c r="K1091" s="1"/>
       <c r="M1091" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1092" spans="4:13" x14ac:dyDescent="0.3">
@@ -30401,7 +30401,7 @@
         <v>64</v>
       </c>
       <c r="H1092" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1092" s="1" t="s">
         <v>13</v>
@@ -30430,7 +30430,7 @@
         <v>65</v>
       </c>
       <c r="H1093" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1093" s="1" t="s">
         <v>10</v>
@@ -30459,7 +30459,7 @@
         <v>116</v>
       </c>
       <c r="H1094" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1094" s="1" t="s">
         <v>10</v>
@@ -30488,7 +30488,7 @@
         <v>69</v>
       </c>
       <c r="H1095" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1095" s="1" t="s">
         <v>10</v>
@@ -30517,7 +30517,7 @@
         <v>70</v>
       </c>
       <c r="H1096" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1096" s="1" t="s">
         <v>10</v>
@@ -30546,7 +30546,7 @@
         <v>71</v>
       </c>
       <c r="H1097" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1097" s="1" t="s">
         <v>10</v>
@@ -30575,7 +30575,7 @@
         <v>120</v>
       </c>
       <c r="H1098" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1098" s="1" t="s">
         <v>10</v>
@@ -30604,7 +30604,7 @@
         <v>99</v>
       </c>
       <c r="H1099" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1099" s="1" t="s">
         <v>10</v>
@@ -30633,7 +30633,7 @@
         <v>72</v>
       </c>
       <c r="H1100" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1100" s="1" t="s">
         <v>10</v>
@@ -30662,7 +30662,7 @@
         <v>75</v>
       </c>
       <c r="H1101" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1101" s="1" t="s">
         <v>10</v>
@@ -30691,7 +30691,7 @@
         <v>77</v>
       </c>
       <c r="H1102" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1102" s="1" t="s">
         <v>13</v>
@@ -30720,7 +30720,7 @@
         <v>78</v>
       </c>
       <c r="H1103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1103" s="1" t="s">
         <v>13</v>
@@ -30749,7 +30749,7 @@
         <v>79</v>
       </c>
       <c r="H1104" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1104" s="1" t="s">
         <v>10</v>
@@ -30778,7 +30778,7 @@
         <v>112</v>
       </c>
       <c r="H1105" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1105" s="1" t="s">
         <v>10</v>
@@ -30807,7 +30807,7 @@
         <v>81</v>
       </c>
       <c r="H1106" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1106" s="1" t="s">
         <v>13</v>
@@ -30836,7 +30836,7 @@
         <v>83</v>
       </c>
       <c r="H1107" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1107" s="1" t="s">
         <v>10</v>
@@ -30865,7 +30865,7 @@
         <v>104</v>
       </c>
       <c r="H1108" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1108" s="1" t="s">
         <v>13</v>
@@ -30894,7 +30894,7 @@
         <v>121</v>
       </c>
       <c r="H1109" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1109" s="1" t="s">
         <v>10</v>
@@ -30923,7 +30923,7 @@
         <v>105</v>
       </c>
       <c r="H1110" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1110" s="1" t="s">
         <v>10</v>
@@ -30952,7 +30952,7 @@
         <v>113</v>
       </c>
       <c r="H1111" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1111" s="1" t="s">
         <v>10</v>
@@ -30981,7 +30981,7 @@
         <v>122</v>
       </c>
       <c r="H1112" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1112" s="1" t="s">
         <v>12</v>
@@ -31005,7 +31005,7 @@
       <c r="J1113" s="2"/>
       <c r="K1113" s="1"/>
       <c r="M1113" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1114" spans="4:13" x14ac:dyDescent="0.3">
@@ -31019,7 +31019,7 @@
         <v>40</v>
       </c>
       <c r="H1114" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1114" s="1" t="s">
         <v>13</v>
@@ -31048,7 +31048,7 @@
         <v>42</v>
       </c>
       <c r="H1115" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1115" s="1" t="s">
         <v>10</v>
@@ -31077,7 +31077,7 @@
         <v>43</v>
       </c>
       <c r="H1116" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1116" s="1" t="s">
         <v>10</v>
@@ -31106,7 +31106,7 @@
         <v>107</v>
       </c>
       <c r="H1117" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1117" s="1" t="s">
         <v>13</v>
@@ -31135,7 +31135,7 @@
         <v>44</v>
       </c>
       <c r="H1118" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1118" s="1" t="s">
         <v>10</v>
@@ -31164,7 +31164,7 @@
         <v>117</v>
       </c>
       <c r="H1119" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1119" s="1" t="s">
         <v>13</v>
@@ -31193,7 +31193,7 @@
         <v>96</v>
       </c>
       <c r="H1120" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1120" s="1" t="s">
         <v>13</v>
@@ -31222,7 +31222,7 @@
         <v>119</v>
       </c>
       <c r="H1121" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1121" s="1" t="s">
         <v>13</v>
@@ -31251,7 +31251,7 @@
         <v>45</v>
       </c>
       <c r="H1122" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1122" s="1" t="s">
         <v>10</v>
@@ -31280,7 +31280,7 @@
         <v>115</v>
       </c>
       <c r="H1123" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1123" s="1" t="s">
         <v>10</v>
@@ -31309,7 +31309,7 @@
         <v>47</v>
       </c>
       <c r="H1124" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1124" s="1" t="s">
         <v>13</v>
@@ -31338,7 +31338,7 @@
         <v>49</v>
       </c>
       <c r="H1125" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1125" s="1" t="s">
         <v>10</v>
@@ -31367,7 +31367,7 @@
         <v>50</v>
       </c>
       <c r="H1126" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1126" s="1" t="s">
         <v>10</v>
@@ -31396,7 +31396,7 @@
         <v>52</v>
       </c>
       <c r="H1127" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1127" s="1" t="s">
         <v>10</v>
@@ -31425,7 +31425,7 @@
         <v>53</v>
       </c>
       <c r="H1128" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1128" s="1" t="s">
         <v>10</v>
@@ -31454,7 +31454,7 @@
         <v>55</v>
       </c>
       <c r="H1129" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1129" s="1" t="s">
         <v>10</v>
@@ -31483,7 +31483,7 @@
         <v>57</v>
       </c>
       <c r="H1130" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1130" s="1" t="s">
         <v>13</v>
@@ -31512,7 +31512,7 @@
         <v>58</v>
       </c>
       <c r="H1131" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1131" s="1" t="s">
         <v>10</v>
@@ -31541,7 +31541,7 @@
         <v>59</v>
       </c>
       <c r="H1132" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1132" s="1" t="s">
         <v>10</v>
@@ -31570,7 +31570,7 @@
         <v>62</v>
       </c>
       <c r="H1133" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1133" s="1" t="s">
         <v>10</v>
@@ -31599,7 +31599,7 @@
         <v>118</v>
       </c>
       <c r="H1134" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1134" s="1" t="s">
         <v>13</v>
@@ -31628,7 +31628,7 @@
         <v>63</v>
       </c>
       <c r="H1135" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1135" s="1" t="s">
         <v>10</v>
@@ -31657,7 +31657,7 @@
         <v>109</v>
       </c>
       <c r="H1136" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1136" s="1" t="s">
         <v>10</v>
@@ -31686,7 +31686,7 @@
         <v>65</v>
       </c>
       <c r="H1137" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1137" s="1" t="s">
         <v>10</v>
@@ -31715,7 +31715,7 @@
         <v>116</v>
       </c>
       <c r="H1138" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1138" s="1" t="s">
         <v>13</v>
@@ -31744,7 +31744,7 @@
         <v>69</v>
       </c>
       <c r="H1139" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1139" s="1" t="s">
         <v>10</v>
@@ -31773,7 +31773,7 @@
         <v>70</v>
       </c>
       <c r="H1140" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1140" s="1" t="s">
         <v>10</v>
@@ -31802,7 +31802,7 @@
         <v>71</v>
       </c>
       <c r="H1141" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1141" s="1" t="s">
         <v>10</v>
@@ -31831,7 +31831,7 @@
         <v>120</v>
       </c>
       <c r="H1142" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1142" s="1" t="s">
         <v>10</v>
@@ -31860,7 +31860,7 @@
         <v>99</v>
       </c>
       <c r="H1143" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1143" s="1" t="s">
         <v>10</v>
@@ -31889,7 +31889,7 @@
         <v>72</v>
       </c>
       <c r="H1144" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1144" s="1" t="s">
         <v>13</v>
@@ -31918,7 +31918,7 @@
         <v>75</v>
       </c>
       <c r="H1145" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1145" s="1" t="s">
         <v>10</v>
@@ -31947,7 +31947,7 @@
         <v>77</v>
       </c>
       <c r="H1146" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1146" s="1" t="s">
         <v>13</v>
@@ -31976,7 +31976,7 @@
         <v>78</v>
       </c>
       <c r="H1147" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1147" s="1" t="s">
         <v>13</v>
@@ -32005,7 +32005,7 @@
         <v>79</v>
       </c>
       <c r="H1148" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1148" s="1" t="s">
         <v>10</v>
@@ -32034,7 +32034,7 @@
         <v>112</v>
       </c>
       <c r="H1149" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1149" s="1" t="s">
         <v>10</v>
@@ -32063,7 +32063,7 @@
         <v>81</v>
       </c>
       <c r="H1150" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1150" s="1" t="s">
         <v>10</v>
@@ -32092,7 +32092,7 @@
         <v>83</v>
       </c>
       <c r="H1151" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1151" s="1" t="s">
         <v>10</v>
@@ -32121,7 +32121,7 @@
         <v>104</v>
       </c>
       <c r="H1152" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1152" s="1" t="s">
         <v>13</v>
@@ -32150,7 +32150,7 @@
         <v>121</v>
       </c>
       <c r="H1153" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1153" s="1" t="s">
         <v>13</v>
@@ -32179,7 +32179,7 @@
         <v>86</v>
       </c>
       <c r="H1154" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1154" s="1" t="s">
         <v>13</v>
@@ -32208,7 +32208,7 @@
         <v>105</v>
       </c>
       <c r="H1155" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1155" s="1" t="s">
         <v>13</v>
@@ -32237,7 +32237,7 @@
         <v>113</v>
       </c>
       <c r="H1156" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1156" s="1" t="s">
         <v>10</v>
@@ -32266,7 +32266,7 @@
         <v>122</v>
       </c>
       <c r="H1157" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1157" s="1" t="s">
         <v>14</v>
@@ -32290,7 +32290,7 @@
       <c r="J1158" s="2"/>
       <c r="K1158" s="1"/>
       <c r="M1158" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1159" spans="4:13" x14ac:dyDescent="0.3">
@@ -32304,7 +32304,7 @@
         <v>40</v>
       </c>
       <c r="H1159" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1159" s="1" t="s">
         <v>13</v>
@@ -32333,7 +32333,7 @@
         <v>42</v>
       </c>
       <c r="H1160" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1160" s="1" t="s">
         <v>13</v>
@@ -32362,7 +32362,7 @@
         <v>43</v>
       </c>
       <c r="H1161" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1161" s="1" t="s">
         <v>10</v>
@@ -32391,7 +32391,7 @@
         <v>107</v>
       </c>
       <c r="H1162" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1162" s="1" t="s">
         <v>10</v>
@@ -32420,7 +32420,7 @@
         <v>44</v>
       </c>
       <c r="H1163" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1163" s="1" t="s">
         <v>10</v>
@@ -32449,7 +32449,7 @@
         <v>117</v>
       </c>
       <c r="H1164" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1164" s="1" t="s">
         <v>13</v>
@@ -32478,7 +32478,7 @@
         <v>96</v>
       </c>
       <c r="H1165" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1165" s="1" t="s">
         <v>13</v>
@@ -32507,7 +32507,7 @@
         <v>119</v>
       </c>
       <c r="H1166" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1166" s="1" t="s">
         <v>13</v>
@@ -32536,7 +32536,7 @@
         <v>45</v>
       </c>
       <c r="H1167" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1167" s="1" t="s">
         <v>10</v>
@@ -32565,7 +32565,7 @@
         <v>115</v>
       </c>
       <c r="H1168" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1168" s="1" t="s">
         <v>10</v>
@@ -32594,7 +32594,7 @@
         <v>47</v>
       </c>
       <c r="H1169" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1169" s="1" t="s">
         <v>13</v>
@@ -32623,7 +32623,7 @@
         <v>49</v>
       </c>
       <c r="H1170" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1170" s="1" t="s">
         <v>10</v>
@@ -32652,7 +32652,7 @@
         <v>50</v>
       </c>
       <c r="H1171" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1171" s="1" t="s">
         <v>10</v>
@@ -32681,7 +32681,7 @@
         <v>52</v>
       </c>
       <c r="H1172" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1172" s="1" t="s">
         <v>10</v>
@@ -32710,7 +32710,7 @@
         <v>53</v>
       </c>
       <c r="H1173" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1173" s="1" t="s">
         <v>10</v>
@@ -32739,7 +32739,7 @@
         <v>55</v>
       </c>
       <c r="H1174" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1174" s="1" t="s">
         <v>10</v>
@@ -32768,7 +32768,7 @@
         <v>57</v>
       </c>
       <c r="H1175" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1175" s="1" t="s">
         <v>13</v>
@@ -32797,7 +32797,7 @@
         <v>58</v>
       </c>
       <c r="H1176" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1176" s="1" t="s">
         <v>13</v>
@@ -32826,7 +32826,7 @@
         <v>59</v>
       </c>
       <c r="H1177" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1177" s="1" t="s">
         <v>13</v>
@@ -32855,7 +32855,7 @@
         <v>62</v>
       </c>
       <c r="H1178" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1178" s="1" t="s">
         <v>10</v>
@@ -32884,7 +32884,7 @@
         <v>118</v>
       </c>
       <c r="H1179" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1179" s="1" t="s">
         <v>13</v>
@@ -32913,7 +32913,7 @@
         <v>63</v>
       </c>
       <c r="H1180" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1180" s="1" t="s">
         <v>10</v>
@@ -32942,7 +32942,7 @@
         <v>109</v>
       </c>
       <c r="H1181" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1181" s="1" t="s">
         <v>13</v>
@@ -32971,7 +32971,7 @@
         <v>65</v>
       </c>
       <c r="H1182" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1182" s="1" t="s">
         <v>10</v>
@@ -33000,7 +33000,7 @@
         <v>116</v>
       </c>
       <c r="H1183" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1183" s="1" t="s">
         <v>13</v>
@@ -33029,7 +33029,7 @@
         <v>69</v>
       </c>
       <c r="H1184" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1184" s="1" t="s">
         <v>10</v>
@@ -33058,7 +33058,7 @@
         <v>70</v>
       </c>
       <c r="H1185" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1185" s="1" t="s">
         <v>10</v>
@@ -33087,7 +33087,7 @@
         <v>71</v>
       </c>
       <c r="H1186" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1186" s="1" t="s">
         <v>10</v>
@@ -33116,7 +33116,7 @@
         <v>120</v>
       </c>
       <c r="H1187" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1187" s="1" t="s">
         <v>13</v>
@@ -33145,7 +33145,7 @@
         <v>99</v>
       </c>
       <c r="H1188" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1188" s="1" t="s">
         <v>10</v>
@@ -33174,7 +33174,7 @@
         <v>72</v>
       </c>
       <c r="H1189" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1189" s="1" t="s">
         <v>10</v>
@@ -33203,7 +33203,7 @@
         <v>75</v>
       </c>
       <c r="H1190" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1190" s="1" t="s">
         <v>10</v>
@@ -33232,7 +33232,7 @@
         <v>77</v>
       </c>
       <c r="H1191" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1191" s="1" t="s">
         <v>10</v>
@@ -33261,7 +33261,7 @@
         <v>78</v>
       </c>
       <c r="H1192" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1192" s="1" t="s">
         <v>13</v>
@@ -33290,7 +33290,7 @@
         <v>79</v>
       </c>
       <c r="H1193" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1193" s="1" t="s">
         <v>12</v>
@@ -33313,7 +33313,7 @@
       <c r="I1194" s="1"/>
       <c r="K1194" s="1"/>
       <c r="M1194" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1195" spans="4:13" x14ac:dyDescent="0.3">
@@ -33327,7 +33327,7 @@
         <v>112</v>
       </c>
       <c r="H1195" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1195" s="1" t="s">
         <v>14</v>
@@ -33351,7 +33351,7 @@
       <c r="J1196" s="2"/>
       <c r="K1196" s="1"/>
       <c r="M1196" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1197" spans="4:13" x14ac:dyDescent="0.3">
@@ -33365,7 +33365,7 @@
         <v>81</v>
       </c>
       <c r="H1197" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1197" s="1" t="s">
         <v>13</v>
@@ -33394,7 +33394,7 @@
         <v>83</v>
       </c>
       <c r="H1198" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1198" s="1" t="s">
         <v>10</v>
@@ -33423,7 +33423,7 @@
         <v>104</v>
       </c>
       <c r="H1199" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1199" s="1" t="s">
         <v>13</v>
@@ -33452,7 +33452,7 @@
         <v>121</v>
       </c>
       <c r="H1200" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1200" s="1" t="s">
         <v>10</v>
@@ -33481,7 +33481,7 @@
         <v>86</v>
       </c>
       <c r="H1201" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1201" s="1" t="s">
         <v>13</v>
@@ -33510,7 +33510,7 @@
         <v>105</v>
       </c>
       <c r="H1202" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1202" s="1" t="s">
         <v>13</v>
@@ -33539,7 +33539,7 @@
         <v>113</v>
       </c>
       <c r="H1203" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1203" s="1" t="s">
         <v>10</v>
@@ -33568,7 +33568,7 @@
         <v>122</v>
       </c>
       <c r="H1204" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1204" s="1" t="s">
         <v>12</v>
@@ -33592,7 +33592,7 @@
       <c r="J1205" s="2"/>
       <c r="K1205" s="1"/>
       <c r="M1205" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1206" spans="4:13" x14ac:dyDescent="0.3">
@@ -33606,7 +33606,7 @@
         <v>40</v>
       </c>
       <c r="H1206" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1206" s="1" t="s">
         <v>13</v>
@@ -33635,7 +33635,7 @@
         <v>42</v>
       </c>
       <c r="H1207" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1207" s="1" t="s">
         <v>13</v>
@@ -33664,7 +33664,7 @@
         <v>43</v>
       </c>
       <c r="H1208" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1208" s="1" t="s">
         <v>10</v>
@@ -33693,7 +33693,7 @@
         <v>107</v>
       </c>
       <c r="H1209" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1209" s="1" t="s">
         <v>13</v>
@@ -33722,7 +33722,7 @@
         <v>44</v>
       </c>
       <c r="H1210" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1210" s="1" t="s">
         <v>10</v>
@@ -33751,7 +33751,7 @@
         <v>117</v>
       </c>
       <c r="H1211" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1211" s="1" t="s">
         <v>13</v>
@@ -33780,7 +33780,7 @@
         <v>96</v>
       </c>
       <c r="H1212" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1212" s="1" t="s">
         <v>13</v>
@@ -33809,7 +33809,7 @@
         <v>119</v>
       </c>
       <c r="H1213" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1213" s="1" t="s">
         <v>13</v>
@@ -33838,7 +33838,7 @@
         <v>45</v>
       </c>
       <c r="H1214" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1214" s="1" t="s">
         <v>10</v>
@@ -33867,7 +33867,7 @@
         <v>115</v>
       </c>
       <c r="H1215" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1215" s="1" t="s">
         <v>10</v>
@@ -33896,7 +33896,7 @@
         <v>47</v>
       </c>
       <c r="H1216" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1216" s="1" t="s">
         <v>10</v>
@@ -33925,7 +33925,7 @@
         <v>49</v>
       </c>
       <c r="H1217" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1217" s="1" t="s">
         <v>10</v>
@@ -33954,7 +33954,7 @@
         <v>50</v>
       </c>
       <c r="H1218" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1218" s="1" t="s">
         <v>10</v>
@@ -33983,7 +33983,7 @@
         <v>52</v>
       </c>
       <c r="H1219" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1219" s="1" t="s">
         <v>10</v>
@@ -34012,7 +34012,7 @@
         <v>53</v>
       </c>
       <c r="H1220" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1220" s="1" t="s">
         <v>10</v>
@@ -34041,7 +34041,7 @@
         <v>55</v>
       </c>
       <c r="H1221" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1221" s="1" t="s">
         <v>10</v>
@@ -34070,7 +34070,7 @@
         <v>57</v>
       </c>
       <c r="H1222" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1222" s="1" t="s">
         <v>13</v>
@@ -34099,7 +34099,7 @@
         <v>58</v>
       </c>
       <c r="H1223" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1223" s="1" t="s">
         <v>10</v>
@@ -34128,7 +34128,7 @@
         <v>59</v>
       </c>
       <c r="H1224" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1224" s="1" t="s">
         <v>13</v>
@@ -34157,7 +34157,7 @@
         <v>62</v>
       </c>
       <c r="H1225" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1225" s="1" t="s">
         <v>10</v>
@@ -34186,7 +34186,7 @@
         <v>118</v>
       </c>
       <c r="H1226" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1226" s="1" t="s">
         <v>13</v>
@@ -34215,7 +34215,7 @@
         <v>63</v>
       </c>
       <c r="H1227" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1227" s="1" t="s">
         <v>13</v>
@@ -34244,7 +34244,7 @@
         <v>109</v>
       </c>
       <c r="H1228" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1228" s="1" t="s">
         <v>10</v>
@@ -34273,7 +34273,7 @@
         <v>65</v>
       </c>
       <c r="H1229" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1229" s="1" t="s">
         <v>10</v>
@@ -34302,7 +34302,7 @@
         <v>116</v>
       </c>
       <c r="H1230" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1230" s="1" t="s">
         <v>13</v>
@@ -34331,7 +34331,7 @@
         <v>69</v>
       </c>
       <c r="H1231" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1231" s="1" t="s">
         <v>10</v>
@@ -34360,7 +34360,7 @@
         <v>70</v>
       </c>
       <c r="H1232" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1232" s="1" t="s">
         <v>12</v>
@@ -34383,7 +34383,7 @@
       <c r="I1233" s="1"/>
       <c r="K1233" s="1"/>
       <c r="M1233" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1234" spans="4:13" x14ac:dyDescent="0.3">
@@ -34397,7 +34397,7 @@
         <v>71</v>
       </c>
       <c r="H1234" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1234" s="1" t="s">
         <v>10</v>
@@ -34426,7 +34426,7 @@
         <v>120</v>
       </c>
       <c r="H1235" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1235" s="1" t="s">
         <v>13</v>
@@ -34455,7 +34455,7 @@
         <v>99</v>
       </c>
       <c r="H1236" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1236" s="1" t="s">
         <v>10</v>
@@ -34484,7 +34484,7 @@
         <v>72</v>
       </c>
       <c r="H1237" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1237" s="1" t="s">
         <v>10</v>
@@ -34513,7 +34513,7 @@
         <v>75</v>
       </c>
       <c r="H1238" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1238" s="1" t="s">
         <v>10</v>
@@ -34542,7 +34542,7 @@
         <v>77</v>
       </c>
       <c r="H1239" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1239" s="1" t="s">
         <v>10</v>
@@ -34571,7 +34571,7 @@
         <v>78</v>
       </c>
       <c r="H1240" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1240" s="1" t="s">
         <v>10</v>
@@ -34600,7 +34600,7 @@
         <v>79</v>
       </c>
       <c r="H1241" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1241" s="1" t="s">
         <v>10</v>
@@ -34629,7 +34629,7 @@
         <v>112</v>
       </c>
       <c r="H1242" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1242" s="1" t="s">
         <v>10</v>
@@ -34658,7 +34658,7 @@
         <v>81</v>
       </c>
       <c r="H1243" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1243" s="1" t="s">
         <v>13</v>
@@ -34687,7 +34687,7 @@
         <v>83</v>
       </c>
       <c r="H1244" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1244" s="1" t="s">
         <v>10</v>
@@ -34716,7 +34716,7 @@
         <v>104</v>
       </c>
       <c r="H1245" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1245" s="1" t="s">
         <v>13</v>
@@ -34745,7 +34745,7 @@
         <v>121</v>
       </c>
       <c r="H1246" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1246" s="1" t="s">
         <v>13</v>
@@ -34774,7 +34774,7 @@
         <v>86</v>
       </c>
       <c r="H1247" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1247" s="1" t="s">
         <v>13</v>
@@ -34803,7 +34803,7 @@
         <v>105</v>
       </c>
       <c r="H1248" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1248" s="1" t="s">
         <v>10</v>
@@ -34832,7 +34832,7 @@
         <v>113</v>
       </c>
       <c r="H1249" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1249" s="1" t="s">
         <v>10</v>
@@ -34861,7 +34861,7 @@
         <v>122</v>
       </c>
       <c r="H1250" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1250" s="1" t="s">
         <v>12</v>
@@ -34885,7 +34885,7 @@
       <c r="J1251" s="2"/>
       <c r="K1251" s="1"/>
       <c r="M1251" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1252" spans="4:13" x14ac:dyDescent="0.3">
@@ -35328,7 +35328,7 @@
       <c r="I1267" s="1"/>
       <c r="K1267" s="1"/>
       <c r="M1267" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1268" spans="4:13" x14ac:dyDescent="0.3">
@@ -35366,7 +35366,7 @@
       <c r="J1269" s="2"/>
       <c r="K1269" s="1"/>
       <c r="M1269" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1270" spans="4:13" x14ac:dyDescent="0.3">
@@ -36337,7 +36337,7 @@
         <v>50</v>
       </c>
       <c r="H1303" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1303" s="1" t="s">
         <v>10</v>
@@ -36366,7 +36366,7 @@
         <v>58</v>
       </c>
       <c r="H1304" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1304" s="1" t="s">
         <v>10</v>
@@ -36395,7 +36395,7 @@
         <v>71</v>
       </c>
       <c r="H1305" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1305" s="1" t="s">
         <v>10</v>
@@ -36424,7 +36424,7 @@
         <v>113</v>
       </c>
       <c r="H1306" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1306" s="1" t="s">
         <v>10</v>
@@ -36453,7 +36453,7 @@
         <v>40</v>
       </c>
       <c r="H1307" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1307" s="1" t="s">
         <v>13</v>
@@ -36482,7 +36482,7 @@
         <v>42</v>
       </c>
       <c r="H1308" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1308" s="1" t="s">
         <v>10</v>
@@ -36511,7 +36511,7 @@
         <v>107</v>
       </c>
       <c r="H1309" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1309" s="1" t="s">
         <v>13</v>
@@ -36540,7 +36540,7 @@
         <v>44</v>
       </c>
       <c r="H1310" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1310" s="1" t="s">
         <v>10</v>
@@ -36569,7 +36569,7 @@
         <v>117</v>
       </c>
       <c r="H1311" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1311" s="1" t="s">
         <v>13</v>
@@ -36598,7 +36598,7 @@
         <v>96</v>
       </c>
       <c r="H1312" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1312" s="1" t="s">
         <v>13</v>
@@ -36627,7 +36627,7 @@
         <v>119</v>
       </c>
       <c r="H1313" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1313" s="1" t="s">
         <v>13</v>
@@ -36656,7 +36656,7 @@
         <v>115</v>
       </c>
       <c r="H1314" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1314" s="1" t="s">
         <v>13</v>
@@ -36685,7 +36685,7 @@
         <v>47</v>
       </c>
       <c r="H1315" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1315" s="1" t="s">
         <v>13</v>
@@ -36714,7 +36714,7 @@
         <v>49</v>
       </c>
       <c r="H1316" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1316" s="1" t="s">
         <v>10</v>
@@ -36743,7 +36743,7 @@
         <v>52</v>
       </c>
       <c r="H1317" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1317" s="1" t="s">
         <v>12</v>
@@ -36767,7 +36767,7 @@
       <c r="J1318" s="2"/>
       <c r="K1318" s="1"/>
       <c r="M1318" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1319" spans="4:13" x14ac:dyDescent="0.3">
@@ -36781,7 +36781,7 @@
         <v>53</v>
       </c>
       <c r="H1319" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1319" s="1" t="s">
         <v>10</v>
@@ -36810,7 +36810,7 @@
         <v>55</v>
       </c>
       <c r="H1320" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1320" s="1" t="s">
         <v>13</v>
@@ -36839,7 +36839,7 @@
         <v>57</v>
       </c>
       <c r="H1321" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1321" s="1" t="s">
         <v>13</v>
@@ -36868,7 +36868,7 @@
         <v>59</v>
       </c>
       <c r="H1322" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1322" s="1" t="s">
         <v>10</v>
@@ -36897,7 +36897,7 @@
         <v>62</v>
       </c>
       <c r="H1323" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1323" s="1" t="s">
         <v>10</v>
@@ -36926,7 +36926,7 @@
         <v>118</v>
       </c>
       <c r="H1324" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1324" s="1" t="s">
         <v>13</v>
@@ -36955,7 +36955,7 @@
         <v>63</v>
       </c>
       <c r="H1325" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1325" s="1" t="s">
         <v>13</v>
@@ -36984,7 +36984,7 @@
         <v>109</v>
       </c>
       <c r="H1326" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1326" s="1" t="s">
         <v>10</v>
@@ -37013,7 +37013,7 @@
         <v>116</v>
       </c>
       <c r="H1327" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1327" s="1" t="s">
         <v>13</v>
@@ -37042,7 +37042,7 @@
         <v>70</v>
       </c>
       <c r="H1328" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1328" s="1" t="s">
         <v>13</v>
@@ -37071,7 +37071,7 @@
         <v>120</v>
       </c>
       <c r="H1329" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1329" s="1" t="s">
         <v>13</v>
@@ -37100,7 +37100,7 @@
         <v>72</v>
       </c>
       <c r="H1330" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1330" s="1" t="s">
         <v>13</v>
@@ -37129,7 +37129,7 @@
         <v>75</v>
       </c>
       <c r="H1331" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1331" s="1" t="s">
         <v>10</v>
@@ -37158,7 +37158,7 @@
         <v>77</v>
       </c>
       <c r="H1332" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1332" s="1" t="s">
         <v>13</v>
@@ -37187,7 +37187,7 @@
         <v>78</v>
       </c>
       <c r="H1333" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1333" s="1" t="s">
         <v>10</v>
@@ -37216,7 +37216,7 @@
         <v>79</v>
       </c>
       <c r="H1334" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1334" s="1" t="s">
         <v>10</v>
@@ -37245,7 +37245,7 @@
         <v>112</v>
       </c>
       <c r="H1335" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1335" s="1" t="s">
         <v>10</v>
@@ -37274,7 +37274,7 @@
         <v>81</v>
       </c>
       <c r="H1336" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1336" s="1" t="s">
         <v>13</v>
@@ -37303,7 +37303,7 @@
         <v>83</v>
       </c>
       <c r="H1337" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1337" s="1" t="s">
         <v>13</v>
@@ -37332,7 +37332,7 @@
         <v>104</v>
       </c>
       <c r="H1338" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1338" s="1" t="s">
         <v>13</v>
@@ -37361,7 +37361,7 @@
         <v>121</v>
       </c>
       <c r="H1339" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1339" s="1" t="s">
         <v>13</v>
@@ -37390,7 +37390,7 @@
         <v>86</v>
       </c>
       <c r="H1340" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1340" s="1" t="s">
         <v>13</v>
@@ -37419,7 +37419,7 @@
         <v>105</v>
       </c>
       <c r="H1341" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1341" s="1" t="s">
         <v>13</v>
@@ -37448,7 +37448,7 @@
         <v>122</v>
       </c>
       <c r="H1342" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1342" s="1" t="s">
         <v>10</v>
@@ -67886,7 +67886,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>